--- a/data_extactor/batch_10_fa/batch_0080_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0080_fa.xlsx
@@ -503,32 +503,32 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Autodesk AutoCAD | نرم‌افزار سیستم مدیریت نگهداری و تعمیرات کامپیوتری CMMS | Cummins INSITE | Dassault Systemes CATIA | Dassault Systemes SolidWorks | نرم‌افزار پایگاه داده | نرم‌افزار عیب‌یابی موتور | نرم‌افزار مدیریت ناوگان | نرم‌افزار ردیابی موجودی | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Word | نرم‌افزار SAP | نرم‌افزار برنامه‌ریزی | نرم‌افزار مدیریت تعمیرگاه</t>
+          <t>Autodesk AutoCAD | Computerized maintenance management system software CMMS | Cummins INSITE | Dassault Systemes CATIA | Dassault Systemes SolidWorks | نرم‌افزار پایگاه داده | نرم‌افزار عیب‌یابی موتور | نرم‌افزار مدیریت ناوگان | نرم‌افزار ردیابی موجودی | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Word | نرم‌افزار SAP | نرم‌افزار زمان‌بندی | نرم‌افزار مدیریت تعمیرگاه</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن گفتن | مانیتورینگ | گوش دادن فعال</t>
+          <t>تفکر انتقادی | سخن گفتن | نظارت | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>مکانیک | حمل و نقل | آموزش و کارآموزی | زبان انگلیسی | ایمنی و امنیت عمومی | ریاضیات | کامپیوتر و الکترونیک | مدیریت و سازماندهی</t>
+          <t>مکانیک | حمل و نقل | آموزش و پرورش | زبان انگلیسی | ایمنی و امنیت عمومی | ریاضیات | رایانه و الکترونیک | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>بینایی نزدیک | ثبات دست و بازو | چالاکی دستی | چالاکی انگشتان | دقت کنترل | حساسیت شنوایی | حساسیت به مسئله | استدلال قیاسی | هماهنگی چند عضو | انعطاف‌پذیری بدنی | قدرت تنه | ترتیب‌دهی اطلاعات | تجسم فضایی | انعطاف‌پذیری بستار | استدلال استقرایی | بیان شفاهی | درک شفاهی | توجه شنوایی | درک عمق | تشخیص گفتار | تشخیص رنگ بصری | بینایی دور | قدرت ایستا | زمان عکس‌العمل | توجه انتخابی | سرعت ادراکی</t>
+          <t>بینایی نزدیک | ثبات دست و بازو | مهارت دستی | مهارت انگشتان | دقت کنترل | حساسیت شنوایی | حساسیت به مسئله | استدلال قیاسی | هماهنگی چند عضو | انعطاف‌پذیری دامنه حرکت | قدرت تنه | ترتیب‌دهی اطلاعات | تجسم | انعطاف‌پذیری بستار | استدلال استقرایی | بیان شفاهی | درک شفاهی | توجه شنیداری | درک عمق | تشخیص گفتار | تشخیص رنگ بصری | بینایی دور | قدرت ایستا | زمان عکس‌العمل | توجه انتخابی | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>قرار گرفتن در معرض آلاینده‌ها | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | پوشیدن تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | درون یک وسیله نقلیه بسته یا کار با تجهیزات بسته | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | سلامت و ایمنی سایر کارکنان | فضاهای داخلی، بدون کنترل شرایط محیطی | اهمیت دقیق یا درست بودن کار | صرف زمان برای خم کردن یا چرخاندن بدن | صرف زمان به صورت ایستاده | قرار گرفتن در معرض فضای کاری تنگ، موقعیت‌های بدنی نامناسب | تاثیر تصمیمات بر همکاران یا نتایج شرکت | فضاهای بیرونی، در معرض تمام شرایط آب و هوایی | قرار گرفتن در معرض تجهیزات خطرناک | تعیین وظایف، اولویت‌ها و اهداف | ارتباط با دیگران | فراوانی تصمیم‌گیری | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | صرف زمان برای انجام حرکات تکراری | آزادی در تصمیم‌گیری | فشار زمانی | صرف زمان برای زانو زدن، چمباتمه زدن، خم شدن یا خزیدن | پیامدهای کاری و نتایج سایر کارکنان | کار با یک گروه کاری یا تیم یا مشارکت در آن | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | مکالمات تلفنی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | صرف زمان برای راه رفتن یا دویدن</t>
+          <t>قرار گرفتن در معرض آلاینده‌ها | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | سلامت و ایمنی سایر کارکنان | محیط داخلی، بدون کنترل شرایط محیطی | اهمیت دقیق یا درست بودن | صرف زمان برای خم کردن یا چرخاندن بدن | صرف زمان برای ایستادن | قرار گرفتن در معرض فضای کاری تنگ، موقعیت‌های بدنی نامناسب | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فضای باز، در معرض تمام شرایط آب و هوایی | قرار گرفتن در معرض تجهیزات خطرناک | تعیین وظایف، اولویت‌ها و اهداف | ارتباط با دیگران | فراوانی تصمیم‌گیری | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | صرف زمان برای انجام حرکات تکراری | آزادی در تصمیم‌گیری | فشار زمانی | صرف زمان برای زانو زدن، چمباتمه زدن، خم شدن یا خزیدن | پیامدهای کاری و نتایج سایر کارکنان | کار با یا مشارکت در یک گروه کاری یا تیم | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | مکالمات تلفنی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | صرف زمان برای راه رفتن یا دویدن</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>مکانیک‌ها و تکنسین‌های خدمات هواپیما | مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | تکنسین‌ها و مکانیک‌های خدمات خودرو | نصب‌کنندگان و تعمیرکنندگان کنترل و شیرآلات، به جز درب‌های مکانیکی | تعمیرکنندگان موتورهای الکتریکی، ابزارهای برقی و موارد مرتبط | مونتاژکنندگان موتور و سایر ماشین‌آلات | مکانیک‌ها و تکنسین‌های خدمات تجهیزات کشاورزی | اپراتورهای بالابر و وینچ | مکانیک‌های ماشین‌آلات صنعتی | اپراتورهای تراکتور و کامیون‌های صنعتی | کارگران نگهداری، ماشین‌آلات | آسیابان‌های صنعتی | مکانیک‌های تجهیزات سنگین متحرک، به جز موتورها | مکانیک‌ها و تکنسین‌های خدمات قایق‌های موتوری | مکانیک‌های موتورسیکلت | مکانیک‌های تجهیزات برق فضای باز و سایر موتورهای کوچک | تعمیرکنندگان واگن‌های ریلی | اپراتورهای ترمز، سیگنال و سوزن راه‌آهن و آتش‌نشانان لوکوموتیو | مهندسان کشتی | مهندسان تاسیسات و اپراتورهای دیگ بخار</t>
+          <t>مکانیک‌ها و تکنسین‌های خدمات هواپیما | مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | تکنسین‌ها و مکانیک‌های خدمات خودرو | نصابان و تعمیرکاران کنترل و شیرآلات، به جز درب‌های مکانیکی | تعمیرکاران موتور الکتریکی، ابزار برقی و موارد مرتبط | مونتاژکاران موتور و سایر ماشین‌آلات | مکانیک‌ها و تکنسین‌های خدمات تجهیزات کشاورزی | اپراتورهای بالابر و وینچ | مکانیک‌های ماشین‌آلات صنعتی | اپراتورهای تراکتور و کامیون صنعتی | کارگران تعمیر و نگهداری ماشین‌آلات | مهندسان نصب ماشین‌آلات | مکانیک‌های تجهیزات سنگین متحرک، به جز موتورها | مکانیک‌ها و تکنسین‌های خدمات قایق‌های موتوری | مکانیک‌های موتورسیکلت | مکانیک‌های تجهیزات برق فضای باز و سایر موتورهای کوچک | تعمیرکنندگان واگن‌های ریلی | اپراتورهای ترمز، علائم و سوزن راه‌آهن و آتش‌کاران لکوموتیو | مهندسان کشتی | مهندسان تاسیسات و اپراتورهای دیگ بخار</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -560,32 +560,32 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>نرم‌افزار سیستم مدیریت نگهداری و تعمیرات کامپیوتری CMMS | FarmLogic FarmPAD | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Word | ServiceMax | نرم‌افزار مرورگر وب</t>
+          <t>سیستم مدیریت نگهداری کامپیوتری CMMS | FarmLogic FarmPAD | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Word | ServiceMax | نرم‌افزار مرورگر وب</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | گوش دادن فعال | سخن گفتن | مانیتورینگ | یادگیری فعال | درک مطلب خواندن</t>
+          <t>تفکر انتقادی | گوش دادن فعال | سخن گفتن | نظارت | یادگیری فعال | درک مطلب</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>مکانیک | خدمات مشتریان و پرسنلی | زبان انگلیسی | کامپیوتر و الکترونیک | مهندسی و فناوری | فیزیک | ریاضیات | تولید و فرآوری</t>
+          <t>مکانیک | خدمات مشتری و شخصی | زبان انگلیسی | رایانه و الکترونیک | مهندسی و فناوری | فیزیک | ریاضیات | تولید و فرآوری</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>چالاکی انگشتان | دقت کنترل | هماهنگی چند عضو | چالاکی دستی | تجسم فضایی | حساسیت به مسئله | بینایی نزدیک | ثبات دست و بازو | استدلال قیاسی | انعطاف‌پذیری بدنی | ترتیب‌دهی اطلاعات | استدلال استقرایی | حساسیت شنوایی | درک کتبی | درک شفاهی | انعطاف‌پذیری بستار | قدرت ایستا | قدرت تنه | تشخیص رنگ بصری | توجه شنوایی | تشخیص گفتار | بیان شفاهی | توجه انتخابی | وضوح گفتار | سرعت ادراکی | جهت‌گیری پاسخ | سرعت بستار | انعطاف‌پذیری دسته‌بندی | بیان کتبی | بینایی دور | سرعت مچ و انگشتان | زمان عکس‌العمل | درک عمق</t>
+          <t>مهارت انگشتان | دقت کنترل | هماهنگی چند عضو | مهارت دستی | تجسم | حساسیت به مسئله | بینایی نزدیک | ثبات دست و بازو | استدلال قیاسی | انعطاف‌پذیری دامنه حرکت | ترتیب‌دهی اطلاعات | استدلال استقرایی | حساسیت شنوایی | درک کتبی | درک شفاهی | انعطاف‌پذیری بستار | قدرت ایستا | قدرت تنه | تشخیص رنگ بصری | توجه شنیداری | تشخیص گفتار | بیان شفاهی | توجه انتخابی | وضوح گفتار | سرعت ادراکی | جهت‌گیری پاسخ | سرعت بستار | انعطاف‌پذیری دسته‌بندی | بیان کتبی | بینایی دور | سرعت مچ و انگشتان | زمان عکس‌العمل | درک عمق</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>پوشیدن تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | آزادی در تصمیم‌گیری | اهمیت دقیق یا درست بودن کار | صرف زمان به صورت ایستاده | ارتباط با دیگران | فضاهای داخلی، بدون کنترل شرایط محیطی | تاثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان برای خم کردن یا چرخاندن بدن | قرار گرفتن در معرض فضای کاری تنگ، موقعیت‌های بدنی نامناسب | فراوانی تصمیم‌گیری | قرار گرفتن در معرض تجهیزات خطرناک | فشار زمانی | کار با یک گروه کاری یا تیم یا مشارکت در آن | صرف زمان برای انجام حرکات تکراری | درون یک وسیله نقلیه روباز یا کار با تجهیزات روباز | سلامت و ایمنی سایر کارکنان | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | تعیین وظایف، اولویت‌ها و اهداف | فضاهای بیرونی، در معرض تمام شرایط آب و هوایی | مکالمات تلفنی | تعامل با مشتریان خارجی یا عموم مردم | صرف زمان برای زانو زدن، چمباتمه زدن، خم شدن یا خزیدن | درون یک وسیله نقلیه بسته یا کار با تجهیزات بسته</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | آزادی در تصمیم‌گیری | اهمیت دقیق یا درست بودن | صرف زمان برای ایستادن | ارتباط با دیگران | محیط داخلی، بدون کنترل شرایط محیطی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان برای خم کردن یا چرخاندن بدن | قرار گرفتن در معرض فضای کاری تنگ، موقعیت‌های بدنی نامناسب | فراوانی تصمیم‌گیری | قرار گرفتن در معرض تجهیزات خطرناک | فشار زمانی | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای انجام حرکات تکراری | در یک وسیله نقلیه روباز یا کار با تجهیزات | سلامت و ایمنی سایر کارکنان | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | تعیین وظایف، اولویت‌ها و اهداف | فضای باز، در معرض تمام شرایط آب و هوایی | مکالمات تلفنی | تعامل با مشتریان خارجی یا عموم مردم | صرف زمان برای زانو زدن، چمباتمه زدن، خم شدن یا خزیدن | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>اپراتورهای تجهیزات کشاورزی | مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | تکنسین‌ها و مکانیک‌های خدمات خودرو | دیگ‌سازان | مکانیک‌های اتوبوس و کامیون و متخصصان موتورهای دیزلی | نصب‌کنندگان و تعمیرکنندگان کنترل و شیرآلات، به جز درب‌های مکانیکی | تعمیرکنندگان موتورهای الکتریکی، ابزارهای برقی و موارد مرتبط | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی تجاری و صنعتی | مونتاژکنندگان موتور و سایر ماشین‌آلات | دستیاران--کارگران نصب، نگهداری و تعمیرات | تکنسین‌های نیروگاه‌های برق‌آبی | مکانیک‌های ماشین‌آلات صنعتی | کارگران نگهداری، ماشین‌آلات | کارگران نگهداری و تعمیرات، عمومی | آسیابان‌های صنعتی | مکانیک‌های تجهیزات سنگین متحرک، به جز موتورها | مکانیک‌ها و تکنسین‌های خدمات قایق‌های موتوری | مکانیک‌های تجهیزات برق فضای باز و سایر موتورهای کوچک | تعمیرکنندگان واگن‌های ریلی | مونتاژکنندگان و تنظیم‌کنندگان ابزارهای زمان‌سنجی</t>
+          <t>اپراتورهای تجهیزات کشاورزی | مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | تکنسین‌ها و مکانیک‌های خدمات خودرو | دیگ‌سازان | مکانیک‌های اتوبوس و کامیون و متخصصان موتورهای دیزلی | نصابان و تعمیرکاران کنترل و شیرآلات، به جز درب‌های مکانیکی | تعمیرکاران موتور الکتریکی، ابزار برقی و موارد مرتبط | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات تجاری و صنعتی | مونتاژکاران موتور و سایر ماشین‌آلات | دستیاران--کارگران نصب، نگهداری و تعمیرات | تکنسین‌های نیروگاه برق‌آبی | مکانیک‌های ماشین‌آلات صنعتی | کارگران تعمیر و نگهداری ماشین‌آلات | کارگران نگهداری و تعمیرات عمومی | مهندسان نصب ماشین‌آلات | مکانیک‌های تجهیزات سنگین متحرک، به جز موتورها | مکانیک‌ها و تکنسین‌های خدمات قایق‌های موتوری | مکانیک‌های تجهیزات برق فضای باز و سایر موتورهای کوچک | تعمیرکنندگان واگن‌های ریلی | مونتاژکاران و تنظیم‌کنندگان دستگاه‌های زمان‌سنجی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -617,32 +617,32 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>نرم‌افزار پایگاه داده | نرم‌افزار مدیریت ناوگان | نرم‌افزار مدیریت نگهداری و تعمیرات | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Word | نرم‌افزار ثبت سوابق</t>
+          <t>نرم‌افزار پایگاه داده | نرم‌افزار مدیریت ناوگان | نرم‌افزار مدیریت تعمیر و نگهداری | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Word | نرم‌افزار ثبت سوابق</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب خواندن | گوش دادن فعال | مانیتورینگ | یادگیری فعال | سخن گفتن | نگارش</t>
+          <t>تفکر انتقادی | درک مطلب | گوش دادن فعال | نظارت | یادگیری فعال | سخن گفتن | نگارش</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>مکانیک | خدمات مشتریان و پرسنلی | ریاضیات | کامپیوتر و الکترونیک | ایمنی و امنیت عمومی</t>
+          <t>مکانیک | خدمات مشتری و شخصی | ریاضیات | رایانه و الکترونیک | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>چالاکی دستی | دقت کنترل | چالاکی انگشتان | انعطاف‌پذیری بدنی | بینایی نزدیک | حساسیت به مسئله | ثبات دست و بازو | هماهنگی چند عضو | تجسم فضایی | زمان عکس‌العمل | ترتیب‌دهی اطلاعات | استدلال قیاسی | استدلال استقرایی | انعطاف‌پذیری بستار | سرعت ادراکی | قدرت ایستا | تشخیص رنگ بصری | بینایی دور | قدرت تنه | کنترل نرخ | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | درک کتبی | بیان شفاهی | درک شفاهی | وضوح گفتار | تشخیص گفتار | توجه شنوایی | حساسیت شنوایی | جهت‌گیری پاسخ</t>
+          <t>مهارت دستی | دقت کنترل | مهارت انگشتان | انعطاف‌پذیری دامنه حرکت | بینایی نزدیک | حساسیت به مسئله | ثبات دست و بازو | هماهنگی چند عضو | تجسم | زمان عکس‌العمل | ترتیب‌دهی اطلاعات | استدلال قیاسی | استدلال استقرایی | انعطاف‌پذیری بستار | سرعت ادراکی | قدرت ایستا | تشخیص رنگ بصری | بینایی دور | قدرت تنه | کنترل نرخ | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | درک کتبی | بیان شفاهی | درک شفاهی | وضوح گفتار | تشخیص گفتار | توجه شنیداری | حساسیت شنوایی | جهت‌گیری پاسخ</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>پوشیدن تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش, محافظ گوش، کلاه ایمنی یا جلیقه نجات | قرار گرفتن در معرض آلاینده‌ها | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | فضاهای داخلی، بدون کنترل شرایط محیطی | قرار گرفتن در معرض تجهیزات خطرناک | فراوانی تصمیم‌گیری | قرار گرفتن در معرض فضای کاری تنگ، موقعیت‌های بدنی نامناسب | فضاهای بیرونی، در معرض تمام شرایط آب و هوایی | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | اهمیت دقیق یا درست بودن کار | مکالمات تلفنی | کار با یک گروه کاری یا تیم یا مشارکت در آن | ارتباط با دیگران | صرف زمان به صورت ایستاده | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | آزادی در تصمیم‌گیری | تاثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان برای خم کردن یا چرخاندن بدن | درون یک وسیله نقلیه بسته یا کار با تجهیزات بسته | سلامت و ایمنی سایر کارکنان | فشار زمانی | ایمیل | صرف زمان برای انجام حرکات تکراری | تعیین وظایف، اولویت‌ها و اهداف | قرار گرفتن در معرض شرایط نوری بسیار روشن یا ناکافی | درون یک وسیله نقلیه روباز یا کار با تجهیزات روباز | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | پیامد خطا | قرار گرفتن در معرض شرایط خطرناک | اهمیت تکرار وظایف مشابه | صرف زمان برای زانو زدن، چمباتمه زدن، خم شدن یا خزیدن | قرار گرفتن در معرض لرزش کل بدن</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | قرار گرفتن در معرض آلاینده‌ها | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | محیط داخلی، بدون کنترل شرایط محیطی | قرار گرفتن در معرض تجهیزات خطرناک | فراوانی تصمیم‌گیری | قرار گرفتن در معرض فضای کاری تنگ، موقعیت‌های بدنی نامناسب | فضای باز، در معرض تمام شرایط آب و هوایی | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | اهمیت دقیق یا درست بودن | مکالمات تلفنی | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | صرف زمان برای ایستادن | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | آزادی در تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان برای خم کردن یا چرخاندن بدن | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | سلامت و ایمنی سایر کارکنان | فشار زمانی | ایمیل | صرف زمان برای انجام حرکات تکراری | تعیین وظایف، اولویت‌ها و اهداف | قرار گرفتن در معرض شرایط نوری بسیار روشن یا ناکافی | در یک وسیله نقلیه روباز یا کار با تجهیزات | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | پیامد خطا | قرار گرفتن در معرض شرایط خطرناک | اهمیت تکرار وظایف یکسان | صرف زمان برای زانو زدن، چمباتمه زدن، خم شدن یا خزیدن | قرار گرفتن در معرض ارتعاش کل بدن</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | تکنسین‌ها و مکانیک‌های خدمات خودرو | مکانیک‌های اتوبوس و کامیون و متخصصان موتورهای دیزلی | نصب‌کنندگان و تعمیرکنندگان کنترل و شیرآلات، به جز درب‌های مکانیکی | اپراتورهای جرثقیل و برجک | تعمیرکنندگان موتورهای الکتریکی، ابزارهای برقی و موارد مرتبط | مونتاژکنندگان موتور و سایر ماشین‌آلات | اپراتورهای ماشین‌های حفاری، بارگیری و دراگ‌لاین، معدن‌کاری سطحی | مکانیک‌ها و تکنسین‌های خدمات تجهیزات کشاورزی | اپراتورهای بالابر و وینچ | مکانیک‌های ماشین‌آلات صنعتی | اپراتورهای تراکتور و کامیون‌های صنعتی | کارگران نگهداری، ماشین‌آلات | کارگران نگهداری و تعمیرات، عمومی | آسیابان‌های صنعتی | مکانیک‌ها و تکنسین‌های خدمات قایق‌های موتوری | مهندسان بهره‌برداری و سایر اپراتورهای تجهیزات ساختمانی | مکانیک‌های تجهیزات برق فضای باز و سایر موتورهای کوچک | تعمیرکنندگان واگن‌های ریلی | دکل‌بندها</t>
+          <t>مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | تکنسین‌ها و مکانیک‌های خدمات خودرو | مکانیک‌های اتوبوس و کامیون و متخصصان موتورهای دیزلی | نصابان و تعمیرکاران کنترل و شیرآلات، به جز درب‌های مکانیکی | اپراتورهای جرثقیل و تاور | تعمیرکاران موتور الکتریکی، ابزار برقی و موارد مرتبط | مونتاژکاران موتور و سایر ماشین‌آلات | اپراتورهای ماشین‌های حفاری و بارگیری و درگ‌لاین، معدن‌کاری سطحی | مکانیک‌ها و تکنسین‌های خدمات تجهیزات کشاورزی | اپراتورهای بالابر و وینچ | مکانیک‌های ماشین‌آلات صنعتی | اپراتورهای تراکتور و کامیون صنعتی | کارگران تعمیر و نگهداری ماشین‌آلات | کارگران نگهداری و تعمیرات عمومی | مهندسان نصب ماشین‌آلات | مکانیک‌ها و تکنسین‌های خدمات قایق‌های موتوری | مهندسان بهره‌برداری و سایر اپراتورهای تجهیزات ساختمانی | مکانیک‌های تجهیزات برق فضای باز و سایر موتورهای کوچک | تعمیرکنندگان واگن‌های ریلی | ریگرها</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Adobe Acrobat | نرم‌افزار دمونتاژ | Microsoft Excel | Microsoft Internet Explorer | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Windows | Microsoft Word | Mozilla Firefox | RailTech Software Solutions Rail 21 Management System | RailTech Software Systems Mars for the 21st Century | WheelShop Automation.com Wheel Shop Management Suite</t>
+          <t>Adobe Acrobat | نرم‌افزار جداسازی | Microsoft Excel | Microsoft Internet Explorer | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Windows | Microsoft Word | Mozilla Firefox | RailTech Software Solutions Rail 21 Management System | RailTech Software Systems Mars for the 21st Century | WheelShop Automation.com Wheel Shop Management Suite</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -684,22 +684,22 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>مکانیک | تولید و فرآوری | طراحی | مدیریت و سازماندهی | ساختمان و ساخت‌وساز | مهندسی و فناوری | حمل و نقل | ریاضیات</t>
+          <t>مکانیک | تولید و فرآوری | طراحی | مدیریت و اداره | ساختمان و ساخت‌وساز | مهندسی و فناوری | حمل و نقل | ریاضیات</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>ثبات دست و بازو | چالاکی دستی | دقت کنترل | هماهنگی چند عضو | چالاکی انگشتان | بینایی نزدیک | حساسیت به مسئله | قدرت تنه | قدرت ایستا | زمان عکس‌العمل | سرعت ادراکی | انعطاف‌پذیری بستار | انعطاف‌پذیری بدنی | بینایی دور | تجسم فضایی | ترتیب‌دهی اطلاعات | استدلال قیاسی | استقامت بدنی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | حساسیت شنوایی | تشخیص رنگ بصری | تعادل عمومی بدن | هماهنگی عمومی بدن | تشخیص گفتار</t>
+          <t>ثبات دست و بازو | مهارت دستی | دقت کنترل | هماهنگی چند عضو | مهارت انگشتان | بینایی نزدیک | حساسیت به مسئله | قدرت تنه | قدرت ایستا | زمان عکس‌العمل | سرعت ادراکی | انعطاف‌پذیری بستار | انعطاف‌پذیری دامنه حرکت | بینایی دور | تجسم | ترتیب‌دهی اطلاعات | استدلال قیاسی | استقامت | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | حساسیت شنوایی | تشخیص رنگ بصری | تعادل کلی بدن | هماهنگی کلی بدن | تشخیص گفتار</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>پوشیدن تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای استفاده از دست‌ها جهت جابجایی, کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان به صورت ایستاده | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض شرایط نوری بسیار روشن یا ناکافی | فضاهای داخلی، بدون کنترل شرایط محیطی | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | فضاهای بیرونی، در معرض تمام شرایط آب و هوایی | آزادی در تصمیم‌گیری | قرار گرفتن در معرض تجهیزات خطرناک | کار با یک گروه کاری یا تیم یا مشارکت در آن | فشار زمانی | ارتباط با دیگران | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | درون یک وسیله نقلیه روباز یا کار با تجهیزات روباز | اهمیت دقیق یا درست بودن کار | تعیین وظایف، اولویت‌ها و اهداف | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | پیامد خطا | نزدیکی فیزیکی | صرف زمان برای راه رفتن یا دویدن | صرف زمان برای خم کردن یا چرخاندن بدن | سلامت و ایمنی سایر کارکنان | پوشیدن تجهیزات محافظتی یا ایمنی تخصصی مانند دستگاه تنفس، مهار ایمنی، لباس‌های محافظ کامل یا محافظت در برابر تشعشع | قرار گرفتن در معرض ارتفاعات بالا</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان برای ایستادن | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض شرایط نوری بسیار روشن یا ناکافی | محیط داخلی، بدون کنترل شرایط محیطی | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | فضای باز، در معرض تمام شرایط آب و هوایی | آزادی در تصمیم‌گیری | قرار گرفتن در معرض تجهیزات خطرناک | کار با یا مشارکت در یک گروه کاری یا تیم | فشار زمانی | ارتباط با دیگران | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | در یک وسیله نقلیه روباز یا کار با تجهیزات | اهمیت دقیق یا درست بودن | تعیین وظایف، اولویت‌ها و اهداف | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | پیامد خطا | نزدیکی فیزیکی | صرف زمان برای راه رفتن یا دویدن | صرف زمان برای خم کردن یا چرخاندن بدن | سلامت و ایمنی سایر کارکنان | استفاده از تجهیزات حفاظتی یا ایمنی تخصصی مانند دستگاه تنفس، هارنس ایمنی، لباس‌های محافظ کامل یا محافظت در برابر تشعشع | قرار گرفتن در معرض ارتفاعات بالا</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>مکانیک‌ها و تکنسین‌های خدمات هواپیما | مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | تعمیرکنندگان بدنه خودرو و موارد مرتبط | تکنسین‌ها و مکانیک‌های خدمات خودرو | مکانیک‌های اتوبوس و کامیون و متخصصان موتورهای دیزلی | نصب‌کنندگان و تعمیرکنندگان کنترل و شیرآلات، به جز درب‌های مکانیکی | تعمیرکنندگان موتورهای الکتریکی، ابزارهای برقی و موارد مرتبط | مونتاژکنندگان موتور و سایر ماشین‌آلات | دستیاران--کارگران نصب، نگهداری و تعمیرات | مکانیک‌های ماشین‌آلات صنعتی | کارگران نگهداری، ماشین‌آلات | کارگران نگهداری و تعمیرات، عمومی | آسیابان‌های صنعتی | مکانیک‌های تجهیزات سنگین متحرک، به جز موتورها | مکانیک‌ها و تکنسین‌های خدمات قایق‌های موتوری | مکانیک‌های موتورسیکلت | مکانیک‌های تجهیزات برق فضای باز و سایر موتورهای کوچک | لوله‌کش‌ها، لوله‌کش‌های صنعتی و بخار | اپراتورهای تجهیزات ریل‌گذاری و نگهداری راه‌آهن | تعمیرکنندگان سیگنال و سوزن راه‌آهن</t>
+          <t>مکانیک‌ها و تکنسین‌های خدمات هواپیما | مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | تعمیرکنندگان بدنه خودرو و موارد مرتبط | تکنسین‌ها و مکانیک‌های خدمات خودرو | مکانیک‌های اتوبوس و کامیون و متخصصان موتورهای دیزلی | نصابان و تعمیرکاران کنترل و شیرآلات، به جز درب‌های مکانیکی | تعمیرکاران موتور الکتریکی، ابزار برقی و موارد مرتبط | مونتاژکاران موتور و سایر ماشین‌آلات | دستیاران--کارگران نصب، نگهداری و تعمیرات | مکانیک‌های ماشین‌آلات صنعتی | کارگران تعمیر و نگهداری ماشین‌آلات | کارگران نگهداری و تعمیرات عمومی | مهندسان نصب ماشین‌آلات | مکانیک‌های تجهیزات سنگین متحرک، به جز موتورها | مکانیک‌ها و تکنسین‌های خدمات قایق‌های موتوری | مکانیک‌های موتورسیکلت | مکانیک‌های تجهیزات برق فضای باز و سایر موتورهای کوچک | لوله‌کش‌ها، لوله‌کش‌های صنعتی و بخار | اپراتورهای تجهیزات ریل‌گذاری و نگهداری خطوط آهن | تعمیرکاران سیگنال و سوزن ریل</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -741,22 +741,22 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>مکانیک | خدمات مشتریان و پرسنلی | کامپیوتر و الکترونیک | زبان انگلیسی | ریاضیات | مهندسی و فناوری | حمل و نقل | مدیریت و سازماندهی | فیزیک</t>
+          <t>مکانیک | خدمات مشتری و شخصی | رایانه و الکترونیک | زبان انگلیسی | ریاضیات | مهندسی و فناوری | حمل و نقل | مدیریت و اداره | فیزیک</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | چالاکی دستی | استدلال قیاسی | استدلال استقرایی | ثبات دست و بازو | چالاکی انگشتان | دقت کنترل | بینایی نزدیک | درک شفاهی | بیان شفاهی | ترتیب‌دهی اطلاعات | هماهنگی چند عضو | حساسیت شنوایی | تشخیص گفتار | انعطاف‌پذیری بدنی | قدرت تنه | تجسم فضایی | قدرت ایستا | توجه انتخابی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | درک عمق | بینایی دور</t>
+          <t>حساسیت به مسئله | مهارت دستی | استدلال قیاسی | استدلال استقرایی | ثبات دست و بازو | مهارت انگشتان | دقت کنترل | بینایی نزدیک | درک شفاهی | بیان شفاهی | ترتیب‌دهی اطلاعات | هماهنگی چند عضو | حساسیت شنوایی | تشخیص گفتار | انعطاف‌پذیری دامنه حرکت | قدرت تنه | تجسم | قدرت ایستا | توجه انتخابی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | درک عمق | بینایی دور</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | فضاهای بیرونی، در معرض تمام شرایط آب و هوایی | درون یک وسیله نقلیه روباز یا کار با تجهیزات روباز | قرار گرفتن در معرض آلاینده‌ها | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | فراوانی تصمیم‌گیری | مکالمات تلفنی | فضاهای داخلی، بدون کنترل شرایط محیطی | آزادی در تصمیم‌گیری | ارتباط با دیگران | صرف زمان به صورت ایستاده | فشار زمانی | قرار گرفتن در معرض فضای کاری تنگ، موقعیت‌های بدنی نامناسب | تاثیر تصمیمات بر همکاران یا نتایج شرکت | فضاهای بیرونی، زیر سرپناه | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | اهمیت دقیق یا درست بودن کار | پوشیدن تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | تعیین وظایف، اولویت‌ها و اهداف | تعامل با مشتریان خارجی یا عموم مردم | قرار گرفتن در معرض تجهیزات خطرناک | کار با یک گروه کاری یا تیم یا مشارکت در آن | قرار گرفتن در معرض شرایط نوری بسیار روشن یا ناکافی | پیامد خطا | نزدیکی فیزیکی</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | فضای باز، در معرض تمام شرایط آب و هوایی | در یک وسیله نقلیه روباز یا کار با تجهیزات | قرار گرفتن در معرض آلاینده‌ها | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | فراوانی تصمیم‌گیری | مکالمات تلفنی | محیط داخلی، بدون کنترل شرایط محیطی | آزادی در تصمیم‌گیری | ارتباط با دیگران | صرف زمان برای ایستادن | فشار زمانی | قرار گرفتن در معرض فضای کاری تنگ، موقعیت‌های بدنی نامناسب | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فضای باز، زیر سقف | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | اهمیت دقیق یا درست بودن | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | تعیین وظایف، اولویت‌ها و اهداف | تعامل با مشتریان خارجی یا عموم مردم | قرار گرفتن در معرض تجهیزات خطرناک | کار با یا مشارکت در یک گروه کاری یا تیم | قرار گرفتن در معرض شرایط نوری بسیار روشن یا ناکافی | پیامد خطا | نزدیکی فیزیکی</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>مکانیک‌ها و تکنسین‌های خدمات هواپیما | مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | تکنسین‌ها و مکانیک‌های خدمات خودرو | تکنسین‌های هوانوردی | مکانیک‌های اتوبوس و کامیون و متخصصان موتورهای دیزلی | نصب‌کنندگان و تعمیرکنندگان کنترل و شیرآلات، به جز درب‌های مکانیکی | تعمیرکنندگان موتورهای الکتریکی، ابزارهای برقی و موارد مرتبط | نصب‌کنندگان و تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات حمل و نقل | مونتاژکنندگان موتور و سایر ماشین‌آلات | مکانیک‌ها و تکنسین‌های خدمات تجهیزات کشاورزی | مکانیک‌های ماشین‌آلات صنعتی | کارگران نگهداری، ماشین‌آلات | مهندسان دریایی و معماران نیروی دریایی | مکانیک‌های تجهیزات سنگین متحرک، به جز موتورها | مکانیک‌های موتورسیکلت | مکانیک‌های تجهیزات برق فضای باز و سایر موتورهای کوچک | تعمیرکنندگان واگن‌های ریلی | تکنسین‌های خدمات وسایل نقلیه تفریحی | دکل‌بندها | مهندسان کشتی</t>
+          <t>مکانیک‌ها و تکنسین‌های خدمات هواپیما | مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | تکنسین‌ها و مکانیک‌های خدمات خودرو | تکنسین‌های هوانوردی | مکانیک‌های اتوبوس و کامیون و متخصصان موتورهای دیزلی | نصابان و تعمیرکاران کنترل و شیرآلات، به جز درب‌های مکانیکی | تعمیرکاران موتور الکتریکی، ابزار برقی و موارد مرتبط | نصب‌کنندگان و تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات حمل و نقل | مونتاژکاران موتور و سایر ماشین‌آلات | مکانیک‌ها و تکنسین‌های خدمات تجهیزات کشاورزی | مکانیک‌های ماشین‌آلات صنعتی | کارگران تعمیر و نگهداری ماشین‌آلات | مهندسان دریایی و معماران کشتی | مکانیک‌های تجهیزات سنگین متحرک، به جز موتورها | مکانیک‌های موتورسیکلت | مکانیک‌های تجهیزات برق فضای باز و سایر موتورهای کوچک | تعمیرکنندگان واگن‌های ریلی | تکنسین‌های خدمات وسایل نقلیه تفریحی | ریگرها | مهندسان کشتی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,27 +793,27 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | سخن گفتن | تفکر انتقادی | یادگیری فعال | مانیتورینگ | درک مطلب خواندن</t>
+          <t>گوش دادن فعال | سخن گفتن | تفکر انتقادی | یادگیری فعال | نظارت | درک مطلب</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>مکانیک | زبان انگلیسی | خدمات مشتریان و پرسنلی | کامپیوتر و الکترونیک | ریاضیات | آموزش و کارآموزی</t>
+          <t>مکانیک | زبان انگلیسی | خدمات مشتری و شخصی | رایانه و الکترونیک | ریاضیات | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>استدلال قیاسی | استدلال استقرایی | چالاکی دستی | چالاکی انگشتان | بینایی نزدیک | حساسیت شنوایی | درک شفاهی | ثبات دست و بازو | حساسیت به مسئله | دقت کنترل | بیان شفاهی | توجه شنوایی | انعطاف‌پذیری بدنی | قدرت تنه | قدرت ایستا | هماهنگی چند عضو | توجه انتخابی | تجسم فضایی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | روان بودن ایده‌ها | وضوح گفتار | تشخیص گفتار | اصالت | درک کتبی</t>
+          <t>استدلال قیاسی | استدلال استقرایی | مهارت دستی | مهارت انگشتان | بینایی نزدیک | حساسیت شنوایی | درک شفاهی | ثبات دست و بازو | حساسیت به مسئله | دقت کنترل | بیان شفاهی | توجه شنیداری | انعطاف‌پذیری دامنه حرکت | قدرت تنه | قدرت ایستا | هماهنگی چند عضو | توجه انتخابی | تجسم | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | روانی ایده‌ها | وضوح گفتار | تشخیص گفتار | اصالت | درک کتبی</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض آلاینده‌ها | فراوانی تصمیم‌گیری | صرف زمان به صورت ایستاده | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | پوشیدن تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | اهمیت دقیق یا درست بودن کار | تاثیر تصمیمات بر همکاران یا نتایج شرکت | پیامد خطا | ارتباط با دیگران | فشار زمانی | کار با یک گروه کاری یا تیم یا مشارکت در آن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای خم کردن یا چرخاندن بدن | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | سلامت و ایمنی سایر کارکنان | صرف زمان برای انجام حرکات تکراری | قرار گرفتن در معرض فضای کاری تنگ، موقعیت‌های بدنی نامناسب | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | صرف زمان برای راه رفتن یا دویدن | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | درون یک وسیله نقلیه روباز یا کار با تجهیزات روباز | اهمیت تکرار وظایف مشابه | صرف زمان برای زانو زدن، چمباتمه زدن، خم شدن یا خزیدن | فضاهای داخلی، با کنترل شرایط محیطی | ایمیل | سطح رقابت | نامه‌ها و یادداشت‌های مکتوب | تعامل با مشتریان خارجی یا عموم مردم | قرار گرفتن در معرض تجهیزات خطرناک | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | فضاهای بیرونی، در معرض تمام شرایط آب و هوایی</t>
+          <t>صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض آلاینده‌ها | فراوانی تصمیم‌گیری | صرف زمان برای ایستادن | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | اهمیت دقیق یا درست بودن | تأثیر تصمیمات بر همکاران یا نتایج شرکت | پیامد خطا | ارتباط با دیگران | فشار زمانی | کار با یا مشارکت در یک گروه کاری یا تیم | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای خم کردن یا چرخاندن بدن | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | سلامت و ایمنی سایر کارکنان | صرف زمان برای انجام حرکات تکراری | قرار گرفتن در معرض فضای کاری تنگ، موقعیت‌های بدنی نامناسب | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | صرف زمان برای راه رفتن یا دویدن | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | در یک وسیله نقلیه روباز یا کار با تجهیزات | اهمیت تکرار وظایف یکسان | صرف زمان برای زانو زدن، چمباتمه زدن، خم شدن یا خزیدن | محیط داخلی، دارای کنترل شرایط محیطی | ایمیل | سطح رقابت | نامه‌ها و یادداشت‌های کتبی | تعامل با مشتریان خارجی یا عموم مردم | قرار گرفتن در معرض تجهیزات خطرناک | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | فضای باز، در معرض تمام شرایط آب و هوایی</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>مکانیک‌ها و تکنسین‌های خدمات هواپیما | مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | تعمیرکنندگان بدنه خودرو و موارد مرتبط | تکنسین‌ها و مکانیک‌های خدمات خودرو | تکنسین‌های هوانوردی | تعمیرکنندگان دوچرخه | مکانیک‌های اتوبوس و کامیون و متخصصان موتورهای دیزلی | نصب‌کنندگان و تعمیرکنندگان کنترل و شیرآلات، به جز درب‌های مکانیکی | تعمیرکنندگان موتورهای الکتریکی، ابزارهای برقی و موارد مرتبط | نصب‌کنندگان و تعمیرکنندگان تجهیزات الکترونیکی، وسایل نقلیه موتوری | مونتاژکنندگان موتور و سایر ماشین‌آلات | مکانیک‌ها و تکنسین‌های خدمات تجهیزات کشاورزی | مکانیک‌های ماشین‌آلات صنعتی | کارگران نگهداری، ماشین‌آلات | مکانیک‌های تجهیزات سنگین متحرک، به جز موتورها | مکانیک‌ها و تکنسین‌های خدمات قایق‌های موتوری | مکانیک‌های تجهیزات برق فضای باز و سایر موتورهای کوچک | تعمیرکنندگان واگن‌های ریلی | تکنسین‌های خدمات وسایل نقلیه تفریحی | تعمیرکنندگان و تعویض‌کنندگان لاستیک</t>
+          <t>مکانیک‌ها و تکنسین‌های خدمات هواپیما | مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | تعمیرکنندگان بدنه خودرو و موارد مرتبط | تکنسین‌ها و مکانیک‌های خدمات خودرو | تکنسین‌های هوانوردی | تعمیرکنندگان دوچرخه | مکانیک‌های اتوبوس و کامیون و متخصصان موتورهای دیزلی | نصابان و تعمیرکاران کنترل و شیرآلات، به جز درب‌های مکانیکی | تعمیرکاران موتور الکتریکی، ابزار برقی و موارد مرتبط | نصب‌کنندگان و تعمیرکنندگان تجهیزات الکترونیکی، وسایل نقلیه موتوری | مونتاژکاران موتور و سایر ماشین‌آلات | مکانیک‌ها و تکنسین‌های خدمات تجهیزات کشاورزی | مکانیک‌های ماشین‌آلات صنعتی | کارگران تعمیر و نگهداری ماشین‌آلات | مکانیک‌های تجهیزات سنگین متحرک، به جز موتورها | مکانیک‌ها و تکنسین‌های خدمات قایق‌های موتوری | مکانیک‌های تجهیزات برق فضای باز و سایر موتورهای کوچک | تعمیرکنندگان واگن‌های ریلی | تکنسین‌های خدمات وسایل نقلیه تفریحی | تعمیرکنندگان و تعویض‌کنندگان لاستیک</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -855,22 +855,22 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>مکانیک | خدمات مشتریان و پرسنلی | زبان انگلیسی | مهندسی و فناوری | آموزش و کارآموزی | حمل و نقل | بازاریابی و فروش</t>
+          <t>مکانیک | خدمات مشتری و شخصی | زبان انگلیسی | مهندسی و فناوری | آموزش و پرورش | حمل و نقل | فروش و بازاریابی</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>چالاکی انگشتان | ثبات دست و بازو | چالاکی دستی | بینایی نزدیک | دقت کنترل | تجسم فضایی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | استدلال قیاسی | انعطاف‌پذیری بدنی | هماهنگی چند عضو | درک شفاهی | بیان شفاهی | توجه انتخابی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | توجه شنوایی | حساسیت شنوایی | قدرت ایستا</t>
+          <t>مهارت انگشتان | ثبات دست و بازو | مهارت دستی | بینایی نزدیک | دقت کنترل | تجسم | ترتیب‌دهی اطلاعات | حساسیت به مسئله | استدلال قیاسی | انعطاف‌پذیری دامنه حرکت | هماهنگی چند عضو | درک شفاهی | بیان شفاهی | توجه انتخابی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | توجه شنیداری | حساسیت شنوایی | قدرت ایستا</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان به صورت ایستاده | ارتباط با دیگران | پوشیدن تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | آزادی در تصمیم‌گیری | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض تجهیزات خطرناک | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | فضاهای داخلی، بدون کنترل شرایط محیطی | تاثیر تصمیمات بر همکاران یا نتایج شرکت | درون یک وسیله نقلیه روباز یا کار با تجهیزات روباز | مکالمات تلفنی | اهمیت دقیق یا درست بودن کار | تعیین وظایف، اولویت‌ها و اهداف | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | فشار زمانی | فضاهای بیرونی، در معرض تمام شرایط آب و هوایی | تعامل با مشتریان خارجی یا عموم مردم</t>
+          <t>صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان برای ایستادن | ارتباط با دیگران | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | آزادی در تصمیم‌گیری | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض تجهیزات خطرناک | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | محیط داخلی، بدون کنترل شرایط محیطی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | در یک وسیله نقلیه روباز یا کار با تجهیزات | مکالمات تلفنی | اهمیت دقیق یا درست بودن | تعیین وظایف، اولویت‌ها و اهداف | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | فشار زمانی | فضای باز، در معرض تمام شرایط آب و هوایی | تعامل با مشتریان خارجی یا عموم مردم</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>مکانیک‌ها و تکنسین‌های خدمات هواپیما | مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | تکنسین‌ها و مکانیک‌های خدمات خودرو | تعمیرکنندگان دوچرخه | مکانیک‌های اتوبوس و کامیون و متخصصان موتورهای دیزلی | تمیزکنندگان وسایل نقلیه و تجهیزات | نصب‌کنندگان و تعمیرکنندگان کنترل و شیرآلات، به جز درب‌های مکانیکی | تعمیرکنندگان موتورهای الکتریکی، ابزارهای برقی و موارد مرتبط | مونتاژکنندگان موتور و سایر ماشین‌آلات | مکانیک‌ها و تکنسین‌های خدمات تجهیزات کشاورزی | تعمیرکنندگان لوازم خانگی | مکانیک‌های ماشین‌آلات صنعتی | اپراتورهای تراکتور و کامیون‌های صنعتی | کارگران نگهداری، ماشین‌آلات | آسیابان‌های صنعتی | مکانیک‌های تجهیزات سنگین متحرک، به جز موتورها | مکانیک‌ها و تکنسین‌های خدمات قایق‌های موتوری | مکانیک‌های موتورسیکلت | تعمیرکنندگان واگن‌های ریلی | سنگ‌زن‌ها، سوهان‌کاران و تیزکنندگان ابزار</t>
+          <t>مکانیک‌ها و تکنسین‌های خدمات هواپیما | مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | تکنسین‌ها و مکانیک‌های خدمات خودرو | تعمیرکنندگان دوچرخه | مکانیک‌های اتوبوس و کامیون و متخصصان موتورهای دیزلی | تمیزکنندگان وسایل نقلیه و تجهیزات | نصابان و تعمیرکاران کنترل و شیرآلات، به جز درب‌های مکانیکی | تعمیرکاران موتور الکتریکی، ابزار برقی و موارد مرتبط | مونتاژکاران موتور و سایر ماشین‌آلات | مکانیک‌ها و تکنسین‌های خدمات تجهیزات کشاورزی | تعمیرکاران لوازم خانگی | مکانیک‌های ماشین‌آلات صنعتی | اپراتورهای تراکتور و کامیون صنعتی | کارگران تعمیر و نگهداری ماشین‌آلات | مهندسان نصب ماشین‌آلات | مکانیک‌های تجهیزات سنگین متحرک، به جز موتورها | مکانیک‌ها و تکنسین‌های خدمات قایق‌های موتوری | مکانیک‌های موتورسیکلت | تعمیرکنندگان واگن‌های ریلی | سنگ‌زنان، سوهان‌کاران و تیزکنندگان ابزار</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,27 +907,27 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | تفکر انتقادی | سخن گفتن | درک مطلب خواندن</t>
+          <t>گوش دادن فعال | تفکر انتقادی | سخن گفتن | درک مطلب</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>مکانیک | خدمات مشتریان و پرسنلی | بازاریابی و فروش | زبان انگلیسی | مهندسی و فناوری | مدیریت و سازماندهی | طراحی | تولید و فرآوری | ریاضیات</t>
+          <t>مکانیک | خدمات مشتری و شخصی | فروش و بازاریابی | زبان انگلیسی | مهندسی و فناوری | مدیریت و اداره | طراحی | تولید و فرآوری | ریاضیات</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>تجسم فضایی | چالاکی انگشتان | بینایی نزدیک | ثبات دست و بازو | چالاکی دستی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | بیان شفاهی | وضوح گفتار | درک شفاهی | تشخیص گفتار | دقت کنترل | درک کتبی | انعطاف‌پذیری بدنی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | استدلال قیاسی</t>
+          <t>تجسم | مهارت انگشتان | بینایی نزدیک | ثبات دست و بازو | مهارت دستی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | بیان شفاهی | وضوح گفتار | درک شفاهی | تشخیص گفتار | دقت کنترل | درک کتبی | انعطاف‌پذیری دامنه حرکت | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | استدلال قیاسی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>مکالمات تلفنی | فضاهای داخلی، با کنترل شرایط محیطی | فراوانی تصمیم‌گیری | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | تعامل با مشتریان خارجی یا عموم مردم | تاثیر تصمیمات بر همکاران یا نتایج شرکت | آزادی در تصمیم‌گیری | فشار زمانی | صرف زمان به صورت ایستاده | اهمیت دقیق یا درست بودن کار | تعیین وظایف، اولویت‌ها و اهداف | ارتباط با دیگران | پوشیدن تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | قرار گرفتن در معرض آلاینده‌ها | ایمیل | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | پیامد خطا | صرف زمان برای انجام حرکات تکراری | نزدیکی فیزیکی</t>
+          <t>مکالمات تلفنی | محیط داخلی، دارای کنترل شرایط محیطی | فراوانی تصمیم‌گیری | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | تعامل با مشتریان خارجی یا عموم مردم | تأثیر تصمیمات بر همکاران یا نتایج شرکت | آزادی در تصمیم‌گیری | فشار زمانی | صرف زمان برای ایستادن | اهمیت دقیق یا درست بودن | تعیین وظایف، اولویت‌ها و اهداف | ارتباط با دیگران | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | قرار گرفتن در معرض آلاینده‌ها | ایمیل | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | پیامد خطا | صرف زمان برای انجام حرکات تکراری | نزدیکی فیزیکی</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | تعمیرکنندگان بدنه خودرو و موارد مرتبط | تکنسین‌ها و مکانیک‌های خدمات خودرو | مکانیک‌های اتوبوس و کامیون و متخصصان موتورهای دیزلی | تعمیرکنندگان موتورهای الکتریکی، ابزارهای برقی و موارد مرتبط | مونتاژکنندگان تجهیزات الکترومکانیکی | مونتاژکنندگان موتور و سایر ماشین‌آلات | مکانیک‌ها و تکنسین‌های خدمات تجهیزات کشاورزی | دستیاران--کارگران نصب، نگهداری و تعمیرات | آسیابان‌های صنعتی | مکانیک‌های تجهیزات سنگین متحرک، به جز موتورها | مکانیک‌ها و تکنسین‌های خدمات قایق‌های موتوری | مکانیک‌های موتورسیکلت | مکانیک‌های تجهیزات برق فضای باز و سایر موتورهای کوچک | تعمیرکنندگان واگن‌های ریلی | تکنسین‌های خدمات وسایل نقلیه تفریحی | دکل‌بندها | کارگران و تعمیرکنندگان کفش و چرم | سازندگان لاستیک | تعمیرکنندگان و تعویض‌کنندگان لاستیک</t>
+          <t>مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | تعمیرکنندگان بدنه خودرو و موارد مرتبط | تکنسین‌ها و مکانیک‌های خدمات خودرو | مکانیک‌های اتوبوس و کامیون و متخصصان موتورهای دیزلی | تعمیرکاران موتور الکتریکی، ابزار برقی و موارد مرتبط | مونتاژکاران تجهیزات الکترومکانیکی | مونتاژکاران موتور و سایر ماشین‌آلات | مکانیک‌ها و تکنسین‌های خدمات تجهیزات کشاورزی | دستیاران--کارگران نصب، نگهداری و تعمیرات | مهندسان نصب ماشین‌آلات | مکانیک‌های تجهیزات سنگین متحرک، به جز موتورها | مکانیک‌ها و تکنسین‌های خدمات قایق‌های موتوری | مکانیک‌های موتورسیکلت | مکانیک‌های تجهیزات برق فضای باز و سایر موتورهای کوچک | تعمیرکنندگان واگن‌های ریلی | تکنسین‌های خدمات وسایل نقلیه تفریحی | ریگرها | کارگران و تعمیرکاران کفش و چرم | تایر سازان | تعمیرکنندگان و تعویض‌کنندگان لاستیک</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,27 +964,27 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>یادگیری فعال | تفکر انتقادی | سخن گفتن | گوش دادن فعال | درک مطلب خواندن</t>
+          <t>یادگیری فعال | تفکر انتقادی | سخن گفتن | گوش دادن فعال | درک مطلب</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>مکانیک | ساختمان و ساخت‌وساز | خدمات مشتریان و پرسنلی | مدیریت و سازماندهی | آموزش و کارآموزی | زبان انگلیسی | مهندسی و فناوری | ریاضیات</t>
+          <t>مکانیک | ساختمان و ساخت‌وساز | خدمات مشتری و شخصی | مدیریت و اداره | آموزش و پرورش | زبان انگلیسی | مهندسی و فناوری | ریاضیات</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>بینایی نزدیک | چالاکی دستی | حساسیت به مسئله | بیان شفاهی | چالاکی انگشتان | دقت کنترل | درک شفاهی | وضوح گفتار | ثبات دست و بازو | ترتیب‌دهی اطلاعات | استدلال قیاسی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | درک کتبی | تشخیص گفتار | انعطاف‌پذیری بدنی | قدرت تنه | هماهنگی چند عضو | تجسم فضایی | سرعت ادراکی</t>
+          <t>بینایی نزدیک | مهارت دستی | حساسیت به مسئله | بیان شفاهی | مهارت انگشتان | دقت کنترل | درک شفاهی | وضوح گفتار | ثبات دست و بازو | ترتیب‌دهی اطلاعات | استدلال قیاسی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | درک کتبی | تشخیص گفتار | انعطاف‌پذیری دامنه حرکت | قدرت تنه | هماهنگی چند عضو | تجسم | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | فضاهای داخلی، بدون کنترل شرایط محیطی | صرف زمان به صورت ایستاده | آزادی در تصمیم‌گیری | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض تجهیزات خطرناک | فراوانی تصمیم‌گیری | ارتباط با دیگران | فضاهای بیرونی، در معرض تمام شرایط آب و هوایی | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن کار | صرف زمان برای زانو زدن، چمباتمه زدن، خم شدن یا خزیدن | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | پوشیدن تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | درون یک وسیله نقلیه بسته یا کار با تجهیزات بسته | تاثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان برای راه رفتن یا دویدن</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، بدون کنترل شرایط محیطی | صرف زمان برای ایستادن | آزادی در تصمیم‌گیری | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض تجهیزات خطرناک | فراوانی تصمیم‌گیری | ارتباط با دیگران | فضای باز، در معرض تمام شرایط آب و هوایی | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | صرف زمان برای زانو زدن، چمباتمه زدن، خم شدن یا خزیدن | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | تأثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان برای راه رفتن یا دویدن</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | تعمیرکنندگان بدنه خودرو و موارد مرتبط | تکنسین‌ها و مکانیک‌های خدمات خودرو | تعمیرکنندگان دوچرخه | مکانیک‌های اتوبوس و کامیون و متخصصان موتورهای دیزلی | تعمیرکنندگان موتورهای الکتریکی، ابزارهای برقی و موارد مرتبط | نصب‌کنندگان و تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات حمل و نقل | نصب‌کنندگان و تعمیرکنندگان تجهیزات الکترونیکی، وسایل نقلیه موتوری | نصب‌کنندگان و تعمیرکنندگان آسانسور و پله برقی | مونتاژکنندگان موتور و سایر ماشین‌آلات | مکانیک‌ها و نصب‌کنندگان گرمایش، تهویه مطبوع و تبرید | دستیاران--کارگران نصب، نگهداری و تعمیرات | تعمیرکنندگان لوازم خانگی | کارگران نگهداری و تعمیرات، عمومی | مکانیک‌های تجهیزات سنگین متحرک، به جز موتورها | مکانیک‌ها و تکنسین‌های خدمات قایق‌های موتوری | مکانیک‌های موتورسیکلت | مکانیک‌های تجهیزات برق فضای باز و سایر موتورهای کوچک | لوله‌کش‌ها، لوله‌کش‌های صنعتی و بخار | تعمیرکنندگان واگن‌های ریلی</t>
+          <t>مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | تعمیرکنندگان بدنه خودرو و موارد مرتبط | تکنسین‌ها و مکانیک‌های خدمات خودرو | تعمیرکنندگان دوچرخه | مکانیک‌های اتوبوس و کامیون و متخصصان موتورهای دیزلی | تعمیرکاران موتور الکتریکی، ابزار برقی و موارد مرتبط | نصب‌کنندگان و تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات حمل و نقل | نصب‌کنندگان و تعمیرکنندگان تجهیزات الکترونیکی، وسایل نقلیه موتوری | نصابان و تعمیرکاران آسانسور و پله برقی | مونتاژکاران موتور و سایر ماشین‌آلات | مکانیک‌ها و نصابان گرمایش، تهویه مطبوع و تبرید | دستیاران--کارگران نصب، نگهداری و تعمیرات | تعمیرکاران لوازم خانگی | کارگران نگهداری و تعمیرات عمومی | مکانیک‌های تجهیزات سنگین متحرک، به جز موتورها | مکانیک‌ها و تکنسین‌های خدمات قایق‌های موتوری | مکانیک‌های موتورسیکلت | مکانیک‌های تجهیزات برق فضای باز و سایر موتورهای کوچک | لوله‌کش‌ها، لوله‌کش‌های صنعتی و بخار | تعمیرکنندگان واگن‌های ریلی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1026,22 +1026,22 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>مکانیک | خدمات مشتریان و پرسنلی | مدیریت و سازماندهی | بازاریابی و فروش</t>
+          <t>مکانیک | خدمات مشتری و شخصی | مدیریت و اداره | فروش و بازاریابی</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>قدرت تنه | چالاکی دستی | هماهنگی چند عضو | قدرت ایستا | بینایی نزدیک | انعطاف‌پذیری بدنی | حساسیت به مسئله | وضوح گفتار | دقت کنترل | چالاکی انگشتان | ثبات دست و بازو | ترتیب‌دهی اطلاعات | استدلال استقرایی | استدلال قیاسی | بیان شفاهی | درک شفاهی</t>
+          <t>قدرت تنه | مهارت دستی | هماهنگی چند عضو | قدرت ایستا | بینایی نزدیک | انعطاف‌پذیری دامنه حرکت | حساسیت به مسئله | وضوح گفتار | دقت کنترل | مهارت انگشتان | ثبات دست و بازو | ترتیب‌دهی اطلاعات | استدلال استقرایی | استدلال قیاسی | بیان شفاهی | درک شفاهی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان به صورت ایستاده | فضاهای داخلی، بدون کنترل شرایط محیطی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن کار | ارتباط با دیگران | کار با یک گروه کاری یا تیم یا مشارکت در آن | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | تعامل با مشتریان خارجی یا عموم مردم | فشار زمانی | فراوانی تصمیم‌گیری | صرف زمان برای خم کردن یا چرخاندن بدن | صرف زمان برای راه رفتن یا دویدن | مکالمات تلفنی | آزادی در تصمیم‌گیری | صرف زمان برای انجام حرکات تکراری | تاثیر تصمیمات بر همکاران یا نتایج شرکت | پوشیدن تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای زانو زدن، چمباتمه زدن، خم شدن یا خزیدن | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | سلامت و ایمنی سایر کارکنان | قرار گرفتن در معرض تجهیزات خطرناک | درون یک وسیله نقلیه بسته یا کار با تجهیزات بسته | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تعیین وظایف، اولویت‌ها و اهداف | پیامد خطا | پیامدهای کاری و نتایج سایر کارکنان | نزدیکی فیزیکی | قرار گرفتن در معرض فضای کاری تنگ، موقعیت‌های بدنی نامناسب</t>
+          <t>صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان برای ایستادن | محیط داخلی، بدون کنترل شرایط محیطی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | تعامل با مشتریان خارجی یا عموم مردم | فشار زمانی | فراوانی تصمیم‌گیری | صرف زمان برای خم کردن یا چرخاندن بدن | صرف زمان برای راه رفتن یا دویدن | مکالمات تلفنی | آزادی در تصمیم‌گیری | صرف زمان برای انجام حرکات تکراری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای زانو زدن، چمباتمه زدن، خم شدن یا خزیدن | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | سلامت و ایمنی سایر کارکنان | قرار گرفتن در معرض تجهیزات خطرناک | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تعیین وظایف، اولویت‌ها و اهداف | پیامد خطا | پیامدهای کاری و نتایج سایر کارکنان | نزدیکی فیزیکی | قرار گرفتن در معرض فضای کاری تنگ، موقعیت‌های بدنی نامناسب</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>تعمیرکنندگان بدنه خودرو و موارد مرتبط | نصب‌کنندگان و تعمیرکنندگان شیشه خودرو | تکنسین‌ها و مکانیک‌های خدمات خودرو | متصدیان خدمات خودرو و شناورها | تعمیرکنندگان دوچرخه | مکانیک‌های اتوبوس و کامیون و متخصصان موتورهای دیزلی | تمیزکنندگان وسایل نقلیه و تجهیزات | نصب‌کنندگان و تعمیرکنندگان کنترل و شیرآلات، به جز درب‌های مکانیکی | تعمیرکنندگان موتورهای الکتریکی، ابزارهای برقی و موارد مرتبط | مونتاژکنندگان موتور و سایر ماشین‌آلات | کارگران دستی سنگ‌زنی و پرداخت | مکانیک‌های ماشین‌آلات صنعتی | اپراتورهای تراکتور و کامیون‌های صنعتی | کارگران نگهداری، ماشین‌آلات | مکانیک‌های تجهیزات سنگین متحرک، به جز موتورها | مکانیک‌های موتورسیکلت | مکانیک‌های تجهیزات برق فضای باز و سایر موتورهای کوچک | تعمیرکنندگان واگن‌های ریلی | اپراتورهای تجهیزات ریل‌گذاری و نگهداری راه‌آهن | سازندگان لاستیک</t>
+          <t>تعمیرکنندگان بدنه خودرو و موارد مرتبط | نصب‌کنندگان و تعمیرکنندگان شیشه خودرو | تکنسین‌ها و مکانیک‌های خدمات خودرو | متصدیان خدمات خودرو و شناورهای آبی | تعمیرکنندگان دوچرخه | مکانیک‌های اتوبوس و کامیون و متخصصان موتورهای دیزلی | تمیزکنندگان وسایل نقلیه و تجهیزات | نصابان و تعمیرکاران کنترل و شیرآلات، به جز درب‌های مکانیکی | تعمیرکاران موتور الکتریکی، ابزار برقی و موارد مرتبط | مونتاژکاران موتور و سایر ماشین‌آلات | کارگران سنگ‌زنی و پرداخت دستی | مکانیک‌های ماشین‌آلات صنعتی | اپراتورهای تراکتور و کامیون صنعتی | کارگران تعمیر و نگهداری ماشین‌آلات | مکانیک‌های تجهیزات سنگین متحرک، به جز موتورها | مکانیک‌های موتورسیکلت | مکانیک‌های تجهیزات برق فضای باز و سایر موتورهای کوچک | تعمیرکنندگان واگن‌های ریلی | اپراتورهای تجهیزات ریل‌گذاری و نگهداری خطوط آهن | تایر سازان</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">

--- a/data_extactor/batch_10_fa/batch_0080_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0080_fa.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن گفتن | نظارت | شنیدن فعال</t>
+          <t>تفکر انتقادی | سخن گفتن | نظارت | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>مکانیک | حمل‌ونقل | آموزش و پرورش | زبان انگلیسی | ایمنی و امنیت عمومی | ریاضیات | رایانه و الکترونیک | مدیریت و امور اداری</t>
+          <t>مکانیک | حمل و نقل | آموزش و پرورش | زبان انگلیسی | ایمنی و امنیت عمومی | ریاضیات | رایانه و الکترونیک | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>دید نزدیک | ثبات دست و بازو | چابکی دستی | چابکی انگشتان | دقت کنترل | حساسیت شنوایی | حساسیت به مسئله | استدلال قیاسی | هماهنگی اندام‌ها | انعطاف‌پذیری گسترده | قدرت بالاتنه | مرتب‌سازی اطلاعات | تجسم فضایی | انعطاف‌پذیری ادراک‌پذیری | استدلال استقرایی | بیان شفاهی | درک شفاهی | توجه شنوایی | درک عمق | تشخیص گفتار | تشخیص تمایز رنگ‌ها | دید دور | قدرت ایستا | زمان واکنش | توجه انتخابی | سرعت ادراک</t>
+          <t>بینایی نزدیک | ثبات دست و بازو | مهارت دستی | مهارت انگشتان | دقت کنترل | حساسیت شنوایی | حساسیت به مسئله | استدلال قیاسی | هماهنگی چند عضو | انعطاف‌پذیری دامنه حرکت | قدرت تنه | ترتیب‌دهی اطلاعات | تجسم | انعطاف‌پذیری بستار | استدلال استقرایی | بیان شفاهی | درک شفاهی | توجه شنیداری | درک عمق | تشخیص گفتار | تشخیص رنگ بصری | بینایی دور | قدرت ایستا | زمان عکس‌العمل | توجه انتخابی | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>مکانیک و تکنسین خدمات هواپیما | مونتاژکار سازه، سطوح و سیستم‌های هواپیما | تکنسین خدمات و مکانیک خودرو | نصاب و تعمیرکار شیرآلات و سیستم‌های کنترل | تعمیرکار موتور برقی، ابزار برقی و تجهیزات وابسته | مونتاژکار موتور و سایر ماشین‌آلات | مکانیک و تکنسین ماشین‌آلات کشاورزی | اپراتور بالابر و وینچ | مکانیک ماشین‌آلات صنعتی | اپراتور لیفتراک و تراکتور صنعتی | کارگر تعمیر و نگهداری ماشین‌آلات | نصاب و مونتاژکار ماشین‌آلات صنعتی (میل‌رایت) | مکانیک تجهیزات سنگین متحرک | مکانیک و تکنسین شناورهای موتوری | مکانیک موتورسیکلت | مکانیک موتورهای کوچک و تجهیزات موتوری فضای باز | تعمیرکار واگن قطار | سوزن‌بان، متصدی ترمز و سیگنال راه‌آهن و آتشکار لوکوموتیو | مهندس کشتی | مهندس موتورخانه و اپراتور دیگ بخار</t>
+          <t>مکانیک و تکنسین خدمات هواپیما | مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | مکانیک و تکنسین خدمات خودرو | نصابان و تعمیرکاران شیرآلات صنعتی و تجهیزات کنترلی | تعمیرکاران موتورهای الکتریکی، ابزارهای برقی و تجهیزات وابسته | مونتاژکاران موتور و سایر ماشین‌آلات | مکانیک و تکنسین خدمات ماشین‌آلات کشاورزی | اپراتورهای بالابر و وینچ | مکانیک‌های ماشین‌آلات صنعتی | رانندگان و اپراتورهای تراکتور و لیفتراک صنعتی | کارگران تعمیر و نگهداری ماشین‌آلات | ماشین‌سازان و متخصصان نصب ماشین‌آلات سنگین [میل‌رایت] | مکانیک تجهیزات سنگین متحرک | مکانیک و تکنسین شناورهای موتوری | مکانیک موتورسیکلت | مکانیک موتورهای کوچک و تجهیزات موتوری فضای باز | تعمیرکار واگن قطار | متصدیان ترمز، علائم و سوزن‌بانی راه‌آهن و آتشکاران لکوموتیو | مهندسان فنی کشتی | مهندسان تأسیسات و اپراتورهای دیگ‌بخار صنعتی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | شنیدن فعال | سخن گفتن | نظارت | یادگیری فعال | درک مطلب</t>
+          <t>تفکر انتقادی | گوش دادن فعال | سخن گفتن | نظارت | یادگیری فعال | درک مطلب</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>مکانیک | خدمات مشتریان و خدمات فردی | زبان انگلیسی | رایانه و الکترونیک | مهندسی و فناوری | فیزیک | ریاضیات | تولید و فرآوری</t>
+          <t>مکانیک | خدمات مشتری و شخصی | زبان انگلیسی | رایانه و الکترونیک | مهندسی و فناوری | فیزیک | ریاضیات | تولید و فرآوری</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>چابکی انگشتان | دقت کنترل | هماهنگی اندام‌ها | چابکی دستی | تجسم فضایی | حساسیت به مسئله | دید نزدیک | ثبات دست و بازو | استدلال قیاسی | انعطاف‌پذیری گسترده | مرتب‌سازی اطلاعات | استدلال استقرایی | حساسیت شنوایی | درک کتبی | درک شفاهی | انعطاف‌پذیری ادراک‌پذیری | قدرت ایستا | قدرت بالاتنه | تشخیص تمایز رنگ‌ها | توجه شنوایی | تشخیص گفتار | بیان شفاهی | توجه انتخابی | وضوح گفتار | سرعت ادراک | جهت‌یابی پاسخ | سرعت ادراک‌پذیری | انعطاف‌پذیری دسته‌بندی | بیان کتبی | دید دور | سرعت مچ و انگشتان | زمان واکنش | درک عمق</t>
+          <t>مهارت انگشتان | دقت کنترل | هماهنگی چند عضو | مهارت دستی | تجسم | حساسیت به مسئله | بینایی نزدیک | ثبات دست و بازو | استدلال قیاسی | انعطاف‌پذیری دامنه حرکت | ترتیب‌دهی اطلاعات | استدلال استقرایی | حساسیت شنوایی | درک کتبی | درک شفاهی | انعطاف‌پذیری بستار | قدرت ایستا | قدرت تنه | تشخیص رنگ بصری | توجه شنیداری | تشخیص گفتار | بیان شفاهی | توجه انتخابی | وضوح گفتار | سرعت ادراکی | جهت‌گیری پاسخ | سرعت بستار | انعطاف‌پذیری دسته‌بندی | بیان کتبی | بینایی دور | سرعت مچ و انگشتان | زمان عکس‌العمل | درک عمق</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>اپراتور ادوات و ماشین‌آلات کشاورزی | مونتاژکار سازه، سطوح و سیستم‌های هواپیما | تکنسین خدمات و مکانیک خودرو | دیگ‌ساز | مکانیک اتوبوس و کامیون و متخصص موتورهای دیزلی | نصاب و تعمیرکار شیرآلات و سیستم‌های کنترل | تعمیرکار موتور برقی، ابزار برقی و تجهیزات وابسته | تعمیرکار تجهیزات الکتریکی و الکترونیکی تجاری و صنعتی | مونتاژکار موتور و سایر ماشین‌آلات | کمک‌کارگر نصب، تعمیر و نگهداری | تکنسین نیروگاه برق‌آبی | مکانیک ماشین‌آلات صنعتی | کارگر تعمیر و نگهداری ماشین‌آلات | کارگر عمومی تعمیر و نگهداری | نصاب و مونتاژکار ماشین‌آلات صنعتی (میل‌رایت) | مکانیک تجهیزات سنگین متحرک | مکانیک و تکنسین شناورهای موتوری | مکانیک موتورهای کوچک و تجهیزات موتوری فضای باز | تعمیرکار واگن قطار | مونتاژکار و تنظیم‌کننده تجهیزات زمان‌سنجی</t>
+          <t>اپراتورهای ماشین‌آلات و ادوات کشاورزی | مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | مکانیک و تکنسین خدمات خودرو | دیگ‌سازان و مخزن‌سازان صنعتی | مکانیک اتوبوس و کامیون و متخصص موتورهای دیزلی | نصابان و تعمیرکاران شیرآلات صنعتی و تجهیزات کنترلی | تعمیرکاران موتورهای الکتریکی، ابزارهای برقی و تجهیزات وابسته | تعمیرکار تجهیزات الکتریکی و الکترونیکی صنعتی و تجاری | مونتاژکاران موتور و سایر ماشین‌آلات | کارگران کمکی نصب، نگهداری و تعمیرات | تکنسین‌های نیروگاه برقابی | مکانیک‌های ماشین‌آلات صنعتی | کارگران تعمیر و نگهداری ماشین‌آلات | کارگران عمومی تعمیرات و نگهداری تاسیسات | ماشین‌سازان و متخصصان نصب ماشین‌آلات سنگین [میل‌رایت] | مکانیک تجهیزات سنگین متحرک | مکانیک و تکنسین شناورهای موتوری | مکانیک موتورهای کوچک و تجهیزات موتوری فضای باز | تعمیرکار واگن قطار | مونتاژکاران و تنظیم‌کنندگان ادوات زمان‌سنجی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | شنیدن فعال | نظارت | یادگیری فعال | سخن گفتن | نگارش</t>
+          <t>تفکر انتقادی | درک مطلب | گوش دادن فعال | نظارت | یادگیری فعال | سخن گفتن | نگارش</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>مکانیک | خدمات مشتریان و خدمات فردی | ریاضیات | رایانه و الکترونیک | ایمنی و امنیت عمومی</t>
+          <t>مکانیک | خدمات مشتری و شخصی | ریاضیات | رایانه و الکترونیک | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>چابکی دستی | دقت کنترل | چابکی انگشتان | انعطاف‌پذیری گسترده | دید نزدیک | حساسیت به مسئله | ثبات دست و بازو | هماهنگی اندام‌ها | تجسم فضایی | زمان واکنش | مرتب‌سازی اطلاعات | استدلال قیاسی | استدلال استقرایی | انعطاف‌پذیری ادراک‌پذیری | سرعت ادراک | قدرت ایستا | تشخیص تمایز رنگ‌ها | دید دور | قدرت بالاتنه | کنترل نرخ | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | درک کتبی | بیان شفاهی | درک شفاهی | وضوح گفتار | تشخیص گفتار | توجه شنوایی | حساسیت شنوایی | جهت‌یابی پاسخ</t>
+          <t>مهارت دستی | دقت کنترل | مهارت انگشتان | انعطاف‌پذیری دامنه حرکت | بینایی نزدیک | حساسیت به مسئله | ثبات دست و بازو | هماهنگی چند عضو | تجسم | زمان عکس‌العمل | ترتیب‌دهی اطلاعات | استدلال قیاسی | استدلال استقرایی | انعطاف‌پذیری بستار | سرعت ادراکی | قدرت ایستا | تشخیص رنگ بصری | بینایی دور | قدرت تنه | کنترل نرخ | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | درک کتبی | بیان شفاهی | درک شفاهی | وضوح گفتار | تشخیص گفتار | توجه شنیداری | حساسیت شنوایی | جهت‌گیری پاسخ</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>مونتاژکار سازه، سطوح و سیستم‌های هواپیما | تکنسین خدمات و مکانیک خودرو | مکانیک اتوبوس و کامیون و متخصص موتورهای دیزلی | نصاب و تعمیرکار شیرآلات و سیستم‌های کنترل | اپراتور جرثقیل و تاورکرین | تعمیرکار موتور برقی، ابزار برقی و تجهیزات وابسته | مونتاژکار موتور و سایر ماشین‌آلات | اپراتور ماشین‌های حفاری و لودر معادن روباز | مکانیک و تکنسین ماشین‌آلات کشاورزی | اپراتور بالابر و وینچ | مکانیک ماشین‌آلات صنعتی | اپراتور لیفتراک و تراکتور صنعتی | کارگر تعمیر و نگهداری ماشین‌آلات | کارگر عمومی تعمیر و نگهداری | نصاب و مونتاژکار ماشین‌آلات صنعتی (میل‌رایت) | مکانیک و تکنسین شناورهای موتوری | اپراتور ماشین‌آلات سنگین راه‌سازی و ساختمانی | مکانیک موتورهای کوچک و تجهیزات موتوری فضای باز | تعمیرکار واگن قطار | ریگر (مسئول باربندی و مهار دکل)</t>
+          <t>مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | مکانیک و تکنسین خدمات خودرو | مکانیک اتوبوس و کامیون و متخصص موتورهای دیزلی | نصابان و تعمیرکاران شیرآلات صنعتی و تجهیزات کنترلی | اپراتورهای جرثقیل و تاورکرین | تعمیرکاران موتورهای الکتریکی، ابزارهای برقی و تجهیزات وابسته | مونتاژکاران موتور و سایر ماشین‌آلات | اپراتورهای ماشین‌آلات حفاری، بارگیری و درگ‌لاین در معادن روباز | مکانیک و تکنسین خدمات ماشین‌آلات کشاورزی | اپراتورهای بالابر و وینچ | مکانیک‌های ماشین‌آلات صنعتی | رانندگان و اپراتورهای تراکتور و لیفتراک صنعتی | کارگران تعمیر و نگهداری ماشین‌آلات | کارگران عمومی تعمیرات و نگهداری تاسیسات | ماشین‌سازان و متخصصان نصب ماشین‌آلات سنگین [میل‌رایت] | مکانیک و تکنسین شناورهای موتوری | اپراتورهای ماشین‌آلات سنگین و تجهیزات عمرانی | مکانیک موتورهای کوچک و تجهیزات موتوری فضای باز | تعمیرکار واگن قطار | ریگرها و تکنسین‌های مهاربندی و جابه‌جایی بار</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | شنیدن فعال | سخن گفتن</t>
+          <t>تفکر انتقادی | گوش دادن فعال | سخن گفتن</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>مکانیک | تولید و فرآوری | طراحی | مدیریت و امور اداری | ساختمان و سازه | مهندسی و فناوری | حمل‌ونقل | ریاضیات</t>
+          <t>مکانیک | تولید و فرآوری | طراحی | مدیریت و اداره | ساختمان و ساخت‌وساز | مهندسی و فناوری | حمل و نقل | ریاضیات</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>ثبات دست و بازو | چابکی دستی | دقت کنترل | هماهنگی اندام‌ها | چابکی انگشتان | دید نزدیک | حساسیت به مسئله | قدرت بالاتنه | قدرت ایستا | زمان واکنش | سرعت ادراک | انعطاف‌پذیری ادراک‌پذیری | انعطاف‌پذیری گسترده | دید دور | تجسم فضایی | مرتب‌سازی اطلاعات | استدلال قیاسی | استقامت بدنی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | حساسیت شنوایی | تشخیص تمایز رنگ‌ها | تعادل عمومی بدن | هماهنگی عمومی بدن | تشخیص گفتار</t>
+          <t>ثبات دست و بازو | مهارت دستی | دقت کنترل | هماهنگی چند عضو | مهارت انگشتان | بینایی نزدیک | حساسیت به مسئله | قدرت تنه | قدرت ایستا | زمان عکس‌العمل | سرعت ادراکی | انعطاف‌پذیری بستار | انعطاف‌پذیری دامنه حرکت | بینایی دور | تجسم | ترتیب‌دهی اطلاعات | استدلال قیاسی | استقامت | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | حساسیت شنوایی | تشخیص رنگ بصری | تعادل کلی بدن | هماهنگی کلی بدن | تشخیص گفتار</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>مکانیک و تکنسین خدمات هواپیما | مونتاژکار سازه، سطوح و سیستم‌های هواپیما | صافکار و نقاش خودرو و تعمیرکار بدنه | تکنسین خدمات و مکانیک خودرو | مکانیک اتوبوس و کامیون و متخصص موتورهای دیزلی | نصاب و تعمیرکار شیرآلات و سیستم‌های کنترل | تعمیرکار موتور برقی، ابزار برقی و تجهیزات وابسته | مونتاژکار موتور و سایر ماشین‌آلات | کمک‌کارگر نصب، تعمیر و نگهداری | مکانیک ماشین‌آلات صنعتی | کارگر تعمیر و نگهداری ماشین‌آلات | کارگر عمومی تعمیر و نگهداری | نصاب و مونتاژکار ماشین‌آلات صنعتی (میل‌رایت) | مکانیک تجهیزات سنگین متحرک | مکانیک و تکنسین شناورهای موتوری | مکانیک موتورسیکلت | مکانیک موتورهای کوچک و تجهیزات موتوری فضای باز | لوله‌کش، تاسیسات‌کار و مونتاژکار لوله‌های بخار | اپراتور ماشین‌آلات ریل‌گذاری و نگهداری خطوط راه‌آهن | تعمیرکار علائم، سوزن و تجهیزات کنترل خطوط ریلی</t>
+          <t>مکانیک و تکنسین خدمات هواپیما | مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | صافکار و نقاش خودرو | مکانیک و تکنسین خدمات خودرو | مکانیک اتوبوس و کامیون و متخصص موتورهای دیزلی | نصابان و تعمیرکاران شیرآلات صنعتی و تجهیزات کنترلی | تعمیرکاران موتورهای الکتریکی، ابزارهای برقی و تجهیزات وابسته | مونتاژکاران موتور و سایر ماشین‌آلات | کارگران کمکی نصب، نگهداری و تعمیرات | مکانیک‌های ماشین‌آلات صنعتی | کارگران تعمیر و نگهداری ماشین‌آلات | کارگران عمومی تعمیرات و نگهداری تاسیسات | ماشین‌سازان و متخصصان نصب ماشین‌آلات سنگین [میل‌رایت] | مکانیک تجهیزات سنگین متحرک | مکانیک و تکنسین شناورهای موتوری | مکانیک موتورسیکلت | مکانیک موتورهای کوچک و تجهیزات موتوری فضای باز | لوله‌کش‌ها، لوله‌کش‌های صنعتی و نصابان خطوط بخار | اپراتورهای ماشین‌آلات روسازی و نگهداری خطوط راه‌آهن | تعمیرکاران علائم، سیگنال‌ها و سوزن‌های راه‌آهن</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | شنیدن فعال | سخن گفتن</t>
+          <t>تفکر انتقادی | گوش دادن فعال | سخن گفتن</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>مکانیک | خدمات مشتریان و خدمات فردی | رایانه و الکترونیک | زبان انگلیسی | ریاضیات | مهندسی و فناوری | حمل‌ونقل | مدیریت و امور اداری | فیزیک</t>
+          <t>مکانیک | خدمات مشتری و شخصی | رایانه و الکترونیک | زبان انگلیسی | ریاضیات | مهندسی و فناوری | حمل و نقل | مدیریت و اداره | فیزیک</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | چابکی دستی | استدلال قیاسی | استدلال استقرایی | ثبات دست و بازو | چابکی انگشتان | دقت کنترل | دید نزدیک | درک شفاهی | بیان شفاهی | مرتب‌سازی اطلاعات | هماهنگی اندام‌ها | حساسیت شنوایی | تشخیص گفتار | انعطاف‌پذیری گسترده | قدرت بالاتنه | تجسم فضایی | قدرت ایستا | توجه انتخابی | انعطاف‌پذیری ادراک‌پذیری | انعطاف‌پذیری دسته‌بندی | درک عمق | دید دور</t>
+          <t>حساسیت به مسئله | مهارت دستی | استدلال قیاسی | استدلال استقرایی | ثبات دست و بازو | مهارت انگشتان | دقت کنترل | بینایی نزدیک | درک شفاهی | بیان شفاهی | ترتیب‌دهی اطلاعات | هماهنگی چند عضو | حساسیت شنوایی | تشخیص گفتار | انعطاف‌پذیری دامنه حرکت | قدرت تنه | تجسم | قدرت ایستا | توجه انتخابی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | درک عمق | بینایی دور</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>مکانیک و تکنسین خدمات هواپیما | مونتاژکار سازه، سطوح و سیستم‌های هواپیما | تکنسین خدمات و مکانیک خودرو | تکنسین اویونیک و الکترونیک هوانوردی | مکانیک اتوبوس و کامیون و متخصص موتورهای دیزلی | نصاب و تعمیرکار شیرآلات و سیستم‌های کنترل | تعمیرکار موتور برقی، ابزار برقی و تجهیزات وابسته | نصاب و تعمیرکار تجهیزات الکتریکی و الکترونیکی ترابری | مونتاژکار موتور و سایر ماشین‌آلات | مکانیک و تکنسین ماشین‌آلات کشاورزی | مکانیک ماشین‌آلات صنعتی | کارگر تعمیر و نگهداری ماشین‌آلات | مهندس شناورهای دریایی و معمار دریایی | مکانیک تجهیزات سنگین متحرک | مکانیک موتورسیکلت | مکانیک موتورهای کوچک و تجهیزات موتوری فضای باز | تعمیرکار واگن قطار | تکنسین خدمات خودروهای کمپر و کاروان | ریگر (مسئول باربندی و مهار دکل) | مهندس کشتی</t>
+          <t>مکانیک و تکنسین خدمات هواپیما | مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | مکانیک و تکنسین خدمات خودرو | تکنسین‌های اویونیک و الکترونیک پرواز | مکانیک اتوبوس و کامیون و متخصص موتورهای دیزلی | نصابان و تعمیرکاران شیرآلات صنعتی و تجهیزات کنترلی | تعمیرکاران موتورهای الکتریکی، ابزارهای برقی و تجهیزات وابسته | نصاب و تعمیرکار تجهیزات الکتریکی و الکترونیکی وسایل نقلیه | مونتاژکاران موتور و سایر ماشین‌آلات | مکانیک و تکنسین خدمات ماشین‌آلات کشاورزی | مکانیک‌های ماشین‌آلات صنعتی | کارگران تعمیر و نگهداری ماشین‌آلات | مهندسان دریایی و معماران کشتی | مکانیک تجهیزات سنگین متحرک | مکانیک موتورسیکلت | مکانیک موتورهای کوچک و تجهیزات موتوری فضای باز | تعمیرکار واگن قطار | تکنسین خدمات خودروهای کمپر و کاروان | ریگرها و تکنسین‌های مهاربندی و جابه‌جایی بار | مهندسان فنی کشتی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | تفکر انتقادی | یادگیری فعال | نظارت | درک مطلب</t>
+          <t>گوش دادن فعال | سخن گفتن | تفکر انتقادی | یادگیری فعال | نظارت | درک مطلب</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>مکانیک | زبان انگلیسی | خدمات مشتریان و خدمات فردی | رایانه و الکترونیک | ریاضیات | آموزش و پرورش</t>
+          <t>مکانیک | زبان انگلیسی | خدمات مشتری و شخصی | رایانه و الکترونیک | ریاضیات | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>استدلال قیاسی | استدلال استقرایی | چابکی دستی | چابکی انگشتان | دید نزدیک | حساسیت شنوایی | درک شفاهی | ثبات دست و بازو | حساسیت به مسئله | دقت کنترل | بیان شفاهی | توجه شنوایی | انعطاف‌پذیری گسترده | قدرت بالاتنه | قدرت ایستا | هماهنگی اندام‌ها | توجه انتخابی | تجسم فضایی | انعطاف‌پذیری دسته‌بندی | مرتب‌سازی اطلاعات | روانی ایده‌ها | وضوح گفتار | تشخیص گفتار | ابتکار و خلاقیت | درک کتبی</t>
+          <t>استدلال قیاسی | استدلال استقرایی | مهارت دستی | مهارت انگشتان | بینایی نزدیک | حساسیت شنوایی | درک شفاهی | ثبات دست و بازو | حساسیت به مسئله | دقت کنترل | بیان شفاهی | توجه شنیداری | انعطاف‌پذیری دامنه حرکت | قدرت تنه | قدرت ایستا | هماهنگی چند عضو | توجه انتخابی | تجسم | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | روانی ایده‌ها | وضوح گفتار | تشخیص گفتار | اصالت | درک کتبی</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>مکانیک و تکنسین خدمات هواپیما | مونتاژکار سازه، سطوح و سیستم‌های هواپیما | صافکار و نقاش خودرو و تعمیرکار بدنه | تکنسین خدمات و مکانیک خودرو | تکنسین اویونیک و الکترونیک هوانوردی | تعمیرکار دوچرخه | مکانیک اتوبوس و کامیون و متخصص موتورهای دیزلی | نصاب و تعمیرکار شیرآلات و سیستم‌های کنترل | تعمیرکار موتور برقی، ابزار برقی و تجهیزات وابسته | نصاب و تعمیرکار تجهیزات الکترونیکی خودرو | مونتاژکار موتور و سایر ماشین‌آلات | مکانیک و تکنسین ماشین‌آلات کشاورزی | مکانیک ماشین‌آلات صنعتی | کارگر تعمیر و نگهداری ماشین‌آلات | مکانیک تجهیزات سنگین متحرک | مکانیک و تکنسین شناورهای موتوری | مکانیک موتورهای کوچک و تجهیزات موتوری فضای باز | تعمیرکار واگن قطار | تکنسین خدمات خودروهای کمپر و کاروان | آپاراتی و پنچرگیر و تعویض‌کار لاستیک</t>
+          <t>مکانیک و تکنسین خدمات هواپیما | مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | صافکار و نقاش خودرو | مکانیک و تکنسین خدمات خودرو | تکنسین‌های اویونیک و الکترونیک پرواز | تعمیرکار دوچرخه | مکانیک اتوبوس و کامیون و متخصص موتورهای دیزلی | نصابان و تعمیرکاران شیرآلات صنعتی و تجهیزات کنترلی | تعمیرکاران موتورهای الکتریکی، ابزارهای برقی و تجهیزات وابسته | نصاب و تعمیرکار تجهیزات الکترونیکی وسایل نقلیه موتوری | مونتاژکاران موتور و سایر ماشین‌آلات | مکانیک و تکنسین خدمات ماشین‌آلات کشاورزی | مکانیک‌های ماشین‌آلات صنعتی | کارگران تعمیر و نگهداری ماشین‌آلات | مکانیک تجهیزات سنگین متحرک | مکانیک و تکنسین شناورهای موتوری | مکانیک موتورهای کوچک و تجهیزات موتوری فضای باز | تعمیرکار واگن قطار | تکنسین خدمات خودروهای کمپر و کاروان | آپاراتی و پنچرگیر و تعویض‌کار لاستیک</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | شنیدن فعال</t>
+          <t>تفکر انتقادی | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>مکانیک | خدمات مشتریان و خدمات فردی | زبان انگلیسی | مهندسی و فناوری | آموزش و پرورش | حمل‌ونقل | فروش و بازاریابی</t>
+          <t>مکانیک | خدمات مشتری و شخصی | زبان انگلیسی | مهندسی و فناوری | آموزش و پرورش | حمل و نقل | فروش و بازاریابی</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>چابکی انگشتان | ثبات دست و بازو | چابکی دستی | دید نزدیک | دقت کنترل | تجسم فضایی | مرتب‌سازی اطلاعات | حساسیت به مسئله | استدلال قیاسی | انعطاف‌پذیری گسترده | هماهنگی اندام‌ها | درک شفاهی | بیان شفاهی | توجه انتخابی | انعطاف‌پذیری ادراک‌پذیری | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | توجه شنوایی | حساسیت شنوایی | قدرت ایستا</t>
+          <t>مهارت انگشتان | ثبات دست و بازو | مهارت دستی | بینایی نزدیک | دقت کنترل | تجسم | ترتیب‌دهی اطلاعات | حساسیت به مسئله | استدلال قیاسی | انعطاف‌پذیری دامنه حرکت | هماهنگی چند عضو | درک شفاهی | بیان شفاهی | توجه انتخابی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | توجه شنیداری | حساسیت شنوایی | قدرت ایستا</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>مکانیک و تکنسین خدمات هواپیما | مونتاژکار سازه، سطوح و سیستم‌های هواپیما | تکنسین خدمات و مکانیک خودرو | تعمیرکار دوچرخه | مکانیک اتوبوس و کامیون و متخصص موتورهای دیزلی | کارگر شست‌وشو و نظافت وسایل نقلیه و تجهیزات | نصاب و تعمیرکار شیرآلات و سیستم‌های کنترل | تعمیرکار موتور برقی، ابزار برقی و تجهیزات وابسته | مونتاژکار موتور و سایر ماشین‌آلات | مکانیک و تکنسین ماشین‌آلات کشاورزی | تعمیرکار لوازم خانگی | مکانیک ماشین‌آلات صنعتی | اپراتور لیفتراک و تراکتور صنعتی | کارگر تعمیر و نگهداری ماشین‌آلات | نصاب و مونتاژکار ماشین‌آلات صنعتی (میل‌رایت) | مکانیک تجهیزات سنگین متحرک | مکانیک و تکنسین شناورهای موتوری | مکانیک موتورسیکلت | تعمیرکار واگن قطار | سنگ‌زن، سوهان‌کار و تیزکننده ابزار</t>
+          <t>مکانیک و تکنسین خدمات هواپیما | مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | مکانیک و تکنسین خدمات خودرو | تعمیرکار دوچرخه | مکانیک اتوبوس و کامیون و متخصص موتورهای دیزلی | شست‌وشوکاران وسایل نقلیه و تجهیزات صنعتی | نصابان و تعمیرکاران شیرآلات صنعتی و تجهیزات کنترلی | تعمیرکاران موتورهای الکتریکی، ابزارهای برقی و تجهیزات وابسته | مونتاژکاران موتور و سایر ماشین‌آلات | مکانیک و تکنسین خدمات ماشین‌آلات کشاورزی | تعمیرکاران لوازم خانگی | مکانیک‌های ماشین‌آلات صنعتی | رانندگان و اپراتورهای تراکتور و لیفتراک صنعتی | کارگران تعمیر و نگهداری ماشین‌آلات | ماشین‌سازان و متخصصان نصب ماشین‌آلات سنگین [میل‌رایت] | مکانیک تجهیزات سنگین متحرک | مکانیک و تکنسین شناورهای موتوری | مکانیک موتورسیکلت | تعمیرکار واگن قطار | سنگ‌زن‌ها، سوهان‌کاران و تیزکاران ابزار</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>شنیدن فعال | تفکر انتقادی | سخن گفتن | درک مطلب</t>
+          <t>گوش دادن فعال | تفکر انتقادی | سخن گفتن | درک مطلب</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>مکانیک | خدمات مشتریان و خدمات فردی | فروش و بازاریابی | زبان انگلیسی | مهندسی و فناوری | مدیریت و امور اداری | طراحی | تولید و فرآوری | ریاضیات</t>
+          <t>مکانیک | خدمات مشتری و شخصی | فروش و بازاریابی | زبان انگلیسی | مهندسی و فناوری | مدیریت و اداره | طراحی | تولید و فرآوری | ریاضیات</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>تجسم فضایی | چابکی انگشتان | دید نزدیک | ثبات دست و بازو | چابکی دستی | مرتب‌سازی اطلاعات | حساسیت به مسئله | بیان شفاهی | وضوح گفتار | درک شفاهی | تشخیص گفتار | دقت کنترل | درک کتبی | انعطاف‌پذیری گسترده | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | استدلال قیاسی</t>
+          <t>تجسم | مهارت انگشتان | بینایی نزدیک | ثبات دست و بازو | مهارت دستی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | بیان شفاهی | وضوح گفتار | درک شفاهی | تشخیص گفتار | دقت کنترل | درک کتبی | انعطاف‌پذیری دامنه حرکت | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | استدلال قیاسی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>مونتاژکار سازه، سطوح و سیستم‌های هواپیما | صافکار و نقاش خودرو و تعمیرکار بدنه | تکنسین خدمات و مکانیک خودرو | مکانیک اتوبوس و کامیون و متخصص موتورهای دیزلی | تعمیرکار موتور برقی، ابزار برقی و تجهیزات وابسته | مونتاژکار تجهیزات الکترومکانیکی | مونتاژکار موتور و سایر ماشین‌آلات | مکانیک و تکنسین ماشین‌آلات کشاورزی | کمک‌کارگر نصب، تعمیر و نگهداری | نصاب و مونتاژکار ماشین‌آلات صنعتی (میل‌رایت) | مکانیک تجهیزات سنگین متحرک | مکانیک و تکنسین شناورهای موتوری | مکانیک موتورسیکلت | مکانیک موتورهای کوچک و تجهیزات موتوری فضای باز | تعمیرکار واگن قطار | تکنسین خدمات خودروهای کمپر و کاروان | ریگر (مسئول باربندی و مهار دکل) | کارگر و تعمیرکار کفش و چرم | سازنده تایر | آپاراتی و پنچرگیر و تعویض‌کار لاستیک</t>
+          <t>مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | صافکار و نقاش خودرو | مکانیک و تکنسین خدمات خودرو | مکانیک اتوبوس و کامیون و متخصص موتورهای دیزلی | تعمیرکاران موتورهای الکتریکی، ابزارهای برقی و تجهیزات وابسته | مونتاژکاران تجهیزات الکترومکانیکی | مونتاژکاران موتور و سایر ماشین‌آلات | مکانیک و تکنسین خدمات ماشین‌آلات کشاورزی | کارگران کمکی نصب، نگهداری و تعمیرات | ماشین‌سازان و متخصصان نصب ماشین‌آلات سنگین [میل‌رایت] | مکانیک تجهیزات سنگین متحرک | مکانیک و تکنسین شناورهای موتوری | مکانیک موتورسیکلت | مکانیک موتورهای کوچک و تجهیزات موتوری فضای باز | تعمیرکار واگن قطار | تکنسین خدمات خودروهای کمپر و کاروان | ریگرها و تکنسین‌های مهاربندی و جابه‌جایی بار | کارگران و تعمیرکاران کفش و چرم | سازندگان تایر | آپاراتی و پنچرگیر و تعویض‌کار لاستیک</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>یادگیری فعال | تفکر انتقادی | سخن گفتن | شنیدن فعال | درک مطلب</t>
+          <t>یادگیری فعال | تفکر انتقادی | سخن گفتن | گوش دادن فعال | درک مطلب</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>مکانیک | ساختمان و سازه | خدمات مشتریان و خدمات فردی | مدیریت و امور اداری | آموزش و پرورش | زبان انگلیسی | مهندسی و فناوری | ریاضیات</t>
+          <t>مکانیک | ساختمان و ساخت‌وساز | خدمات مشتری و شخصی | مدیریت و اداره | آموزش و پرورش | زبان انگلیسی | مهندسی و فناوری | ریاضیات</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>دید نزدیک | چابکی دستی | حساسیت به مسئله | بیان شفاهی | چابکی انگشتان | دقت کنترل | درک شفاهی | وضوح گفتار | ثبات دست و بازو | مرتب‌سازی اطلاعات | استدلال قیاسی | انعطاف‌پذیری ادراک‌پذیری | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | درک کتبی | تشخیص گفتار | انعطاف‌پذیری گسترده | قدرت بالاتنه | هماهنگی اندام‌ها | تجسم فضایی | سرعت ادراک</t>
+          <t>بینایی نزدیک | مهارت دستی | حساسیت به مسئله | بیان شفاهی | مهارت انگشتان | دقت کنترل | درک شفاهی | وضوح گفتار | ثبات دست و بازو | ترتیب‌دهی اطلاعات | استدلال قیاسی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | درک کتبی | تشخیص گفتار | انعطاف‌پذیری دامنه حرکت | قدرت تنه | هماهنگی چند عضو | تجسم | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>مونتاژکار سازه، سطوح و سیستم‌های هواپیما | صافکار و نقاش خودرو و تعمیرکار بدنه | تکنسین خدمات و مکانیک خودرو | تعمیرکار دوچرخه | مکانیک اتوبوس و کامیون و متخصص موتورهای دیزلی | تعمیرکار موتور برقی، ابزار برقی و تجهیزات وابسته | نصاب و تعمیرکار تجهیزات الکتریکی و الکترونیکی ترابری | نصاب و تعمیرکار تجهیزات الکترونیکی خودرو | نصاب و تعمیرکار آسانسور و پله‌برقی | مونتاژکار موتور و سایر ماشین‌آلات | مکانیک و نصاب تاسیسات سرمایشی، گرمایشی و تهویه مطبوع | کمک‌کارگر نصب، تعمیر و نگهداری | تعمیرکار لوازم خانگی | کارگر عمومی تعمیر و نگهداری | مکانیک تجهیزات سنگین متحرک | مکانیک و تکنسین شناورهای موتوری | مکانیک موتورسیکلت | مکانیک موتورهای کوچک و تجهیزات موتوری فضای باز | لوله‌کش، تاسیسات‌کار و مونتاژکار لوله‌های بخار | تعمیرکار واگن قطار</t>
+          <t>مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | صافکار و نقاش خودرو | مکانیک و تکنسین خدمات خودرو | تعمیرکار دوچرخه | مکانیک اتوبوس و کامیون و متخصص موتورهای دیزلی | تعمیرکاران موتورهای الکتریکی، ابزارهای برقی و تجهیزات وابسته | نصاب و تعمیرکار تجهیزات الکتریکی و الکترونیکی وسایل نقلیه | نصاب و تعمیرکار تجهیزات الکترونیکی وسایل نقلیه موتوری | نصابان و تعمیرکاران آسانسور و پله‌برقی | مونتاژکاران موتور و سایر ماشین‌آلات | مکانیک‌ها و نصابان سیستم‌های گرمایشی، تهویه مطبوع و تبرید | کارگران کمکی نصب، نگهداری و تعمیرات | تعمیرکاران لوازم خانگی | کارگران عمومی تعمیرات و نگهداری تاسیسات | مکانیک تجهیزات سنگین متحرک | مکانیک و تکنسین شناورهای موتوری | مکانیک موتورسیکلت | مکانیک موتورهای کوچک و تجهیزات موتوری فضای باز | لوله‌کش‌ها، لوله‌کش‌های صنعتی و نصابان خطوط بخار | تعمیرکار واگن قطار</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1016,22 +1016,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>نرم‌افزار برآورد و تخمین هزینه‌ها | نرم‌افزار ثبت سوابق فنی | Microsoft Excel | Microsoft Outlook | Microsoft Word</t>
+          <t>نرم‌افزار برآورد و تخمین هزینه‌ها | نرم‌افزار ثبت سوابق فنی | Microsoft Excel | Microsoft Outlook | نرم‌افزار ثبت سوابق</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن گفتن | شنیدن فعال</t>
+          <t>تفکر انتقادی | سخن گفتن | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>مکانیک | خدمات مشتریان و خدمات فردی | مدیریت و امور اداری | فروش و بازاریابی</t>
+          <t>مکانیک | خدمات مشتری و شخصی | مدیریت و اداره | فروش و بازاریابی</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>قدرت بالاتنه | چابکی دستی | هماهنگی اندام‌ها | قدرت ایستا | دید نزدیک | انعطاف‌پذیری گسترده | حساسیت به مسئله | وضوح گفتار | دقت کنترل | چابکی انگشتان | ثبات دست و بازو | مرتب‌سازی اطلاعات | استدلال استقرایی | استدلال قیاسی | بیان شفاهی | درک شفاهی</t>
+          <t>قدرت تنه | مهارت دستی | هماهنگی چند عضو | قدرت ایستا | بینایی نزدیک | انعطاف‌پذیری دامنه حرکت | حساسیت به مسئله | وضوح گفتار | دقت کنترل | مهارت انگشتان | ثبات دست و بازو | ترتیب‌دهی اطلاعات | استدلال استقرایی | استدلال قیاسی | بیان شفاهی | درک شفاهی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>صافکار و نقاش خودرو و تعمیرکار بدنه | نصاب و تعمیرکار شیشه خودرو | تکنسین خدمات و مکانیک خودرو | متصدی خدمات خودرو و شناورها | تعمیرکار دوچرخه | مکانیک اتوبوس و کامیون و متخصص موتورهای دیزلی | کارگر شست‌وشو و نظافت وسایل نقلیه و تجهیزات | نصاب و تعمیرکار شیرآلات و سیستم‌های کنترل | تعمیرکار موتور برقی، ابزار برقی و تجهیزات وابسته | مونتاژکار موتور و سایر ماشین‌آلات | پرداخت‌کار و پولیش‌کار دستی فلزات | مکانیک ماشین‌آلات صنعتی | اپراتور لیفتراک و تراکتور صنعتی | کارگر تعمیر و نگهداری ماشین‌آلات | مکانیک تجهیزات سنگین متحرک | مکانیک موتورسیکلت | مکانیک موتورهای کوچک و تجهیزات موتوری فضای باز | تعمیرکار واگن قطار | اپراتور ماشین‌آلات ریل‌گذاری و نگهداری خطوط راه‌آهن | سازنده تایر</t>
+          <t>صافکار و نقاش خودرو | نصاب و تعمیرکار شیشه خودرو | مکانیک و تکنسین خدمات خودرو | متصدیان جایگاه‌های سوخت و خدمات وسایل نقلیه و شناورها | تعمیرکار دوچرخه | مکانیک اتوبوس و کامیون و متخصص موتورهای دیزلی | شست‌وشوکاران وسایل نقلیه و تجهیزات صنعتی | نصابان و تعمیرکاران شیرآلات صنعتی و تجهیزات کنترلی | تعمیرکاران موتورهای الکتریکی، ابزارهای برقی و تجهیزات وابسته | مونتاژکاران موتور و سایر ماشین‌آلات | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | مکانیک‌های ماشین‌آلات صنعتی | رانندگان و اپراتورهای تراکتور و لیفتراک صنعتی | کارگران تعمیر و نگهداری ماشین‌آلات | مکانیک تجهیزات سنگین متحرک | مکانیک موتورسیکلت | مکانیک موتورهای کوچک و تجهیزات موتوری فضای باز | تعمیرکار واگن قطار | اپراتورهای ماشین‌آلات روسازی و نگهداری خطوط راه‌آهن | سازندگان تایر</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
